--- a/database/event/1886/event_1886_evp_summary.xlsx
+++ b/database/event/1886/event_1886_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1.4815</v>
+        <v>1.4326</v>
       </c>
       <c r="E2" t="n">
         <v>4.7102</v>
@@ -548,7 +548,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8974</v>
+        <v>0.8566</v>
       </c>
       <c r="E3" t="n">
         <v>3.2644</v>
@@ -594,7 +594,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8699</v>
+        <v>0.8295</v>
       </c>
       <c r="E4" t="n">
         <v>3.1964</v>
@@ -640,7 +640,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.672</v>
       </c>
       <c r="E5" t="n">
         <v>2.801</v>
@@ -686,7 +686,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6277</v>
+        <v>0.5907</v>
       </c>
       <c r="E6" t="n">
         <v>2.5969</v>
@@ -732,7 +732,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4169</v>
+        <v>0.3828</v>
       </c>
       <c r="E7" t="n">
         <v>2.0751</v>
@@ -778,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0232</v>
+        <v>-0.0512</v>
       </c>
       <c r="E8" t="n">
         <v>0.9856</v>
@@ -824,7 +824,7 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3016</v>
+        <v>-0.3258</v>
       </c>
       <c r="E9" t="n">
         <v>0.2965</v>
@@ -870,7 +870,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3981</v>
+        <v>-0.421</v>
       </c>
       <c r="E10" t="n">
         <v>0.0576</v>
@@ -916,7 +916,7 @@
         <v>-0</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.6454</v>
+        <v>-0.6649</v>
       </c>
       <c r="E11" t="n">
         <v>-0.5547</v>
@@ -962,7 +962,7 @@
         <v>-0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.6708</v>
+        <v>-0.6899</v>
       </c>
       <c r="E12" t="n">
         <v>-0.6175</v>
@@ -1008,7 +1008,7 @@
         <v>-0</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.6763</v>
+        <v>-0.6953</v>
       </c>
       <c r="E13" t="n">
         <v>-0.631</v>
@@ -1054,7 +1054,7 @@
         <v>-0</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.7917999999999999</v>
+        <v>-0.8092</v>
       </c>
       <c r="E14" t="n">
         <v>-0.917</v>
@@ -1100,7 +1100,7 @@
         <v>-0</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.834</v>
+        <v>-0.8508</v>
       </c>
       <c r="E15" t="n">
         <v>-1.0214</v>
@@ -1146,7 +1146,7 @@
         <v>-0</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.9176</v>
+        <v>-0.9333</v>
       </c>
       <c r="E16" t="n">
         <v>-1.2284</v>
@@ -1192,7 +1192,7 @@
         <v>-0</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.9325</v>
+        <v>-0.948</v>
       </c>
       <c r="E17" t="n">
         <v>-1.2652</v>
@@ -1238,7 +1238,7 @@
         <v>-0</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1086</v>
+        <v>-1.1217</v>
       </c>
       <c r="E18" t="n">
         <v>-1.7013</v>
@@ -1284,7 +1284,7 @@
         <v>-0</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1355</v>
+        <v>-1.1482</v>
       </c>
       <c r="E19" t="n">
         <v>-1.7677</v>
@@ -1330,7 +1330,7 @@
         <v>-0</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2151</v>
+        <v>-1.2266</v>
       </c>
       <c r="E20" t="n">
         <v>-1.9647</v>
@@ -1376,7 +1376,7 @@
         <v>-0</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8061</v>
+        <v>-1.8095</v>
       </c>
       <c r="E21" t="n">
         <v>-3.4277</v>

--- a/database/event/1886/event_1886_evp_summary.xlsx
+++ b/database/event/1886/event_1886_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.7102</v>
+        <v>4.6507</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1.4326</v>
+        <v>1.4615</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7102</v>
+        <v>4.6507</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1772</v>
+        <v>2.5793</v>
       </c>
       <c r="G2" t="n">
-        <v>2.533</v>
+        <v>2.0714</v>
       </c>
       <c r="H2" t="n">
-        <v>2.1772</v>
+        <v>3.6015</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7647</v>
+        <v>1.8726</v>
       </c>
       <c r="J2" t="n">
-        <v>2.533</v>
+        <v>2.0714</v>
       </c>
       <c r="K2" t="n">
         <v>58</v>
@@ -529,7 +529,7 @@
         <v>85</v>
       </c>
       <c r="M2" t="n">
-        <v>4.2977</v>
+        <v>3.944</v>
       </c>
       <c r="N2" t="n">
         <v>143</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.2644</v>
+        <v>3.4841</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8566</v>
+        <v>0.9349</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2644</v>
+        <v>3.4841</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5754</v>
+        <v>1.1826</v>
       </c>
       <c r="G3" t="n">
-        <v>2.689</v>
+        <v>2.3015</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5754</v>
+        <v>1.1826</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4664</v>
+        <v>0.6149</v>
       </c>
       <c r="J3" t="n">
-        <v>2.689</v>
+        <v>2.3015</v>
       </c>
       <c r="K3" t="n">
         <v>114</v>
@@ -575,7 +575,7 @@
         <v>84</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1554</v>
+        <v>2.9164</v>
       </c>
       <c r="N3" t="n">
         <v>198</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.1964</v>
+        <v>3.2917</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8295</v>
+        <v>0.848</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1964</v>
+        <v>3.2917</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7002</v>
+        <v>2.8453</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4962</v>
+        <v>0.4464</v>
       </c>
       <c r="H4" t="n">
-        <v>2.7002</v>
+        <v>4.5389</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1886</v>
+        <v>2.36</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4962</v>
+        <v>0.4464</v>
       </c>
       <c r="K4" t="n">
         <v>132</v>
@@ -621,7 +621,7 @@
         <v>56</v>
       </c>
       <c r="M4" t="n">
-        <v>2.6848</v>
+        <v>2.8064</v>
       </c>
       <c r="N4" t="n">
         <v>188</v>
@@ -630,93 +630,93 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.801</v>
+        <v>2.7328</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.672</v>
+        <v>0.5957</v>
       </c>
       <c r="E5" t="n">
-        <v>2.801</v>
+        <v>2.7328</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2068</v>
+        <v>2.5215</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5942</v>
+        <v>0.2113</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2068</v>
+        <v>3.398</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1676</v>
+        <v>1.7668</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5942</v>
+        <v>0.2113</v>
       </c>
       <c r="K5" t="n">
-        <v>114</v>
+        <v>58</v>
       </c>
       <c r="L5" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M5" t="n">
-        <v>2.7618</v>
+        <v>1.9781</v>
       </c>
       <c r="N5" t="n">
-        <v>198</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.5969</v>
+        <v>2.64</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5907</v>
+        <v>0.5538</v>
       </c>
       <c r="E6" t="n">
-        <v>2.5969</v>
+        <v>2.64</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1554</v>
+        <v>0.422</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4415</v>
+        <v>2.218</v>
       </c>
       <c r="H6" t="n">
-        <v>2.1554</v>
+        <v>0.422</v>
       </c>
       <c r="I6" t="n">
-        <v>1.747</v>
+        <v>0.2194</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4415</v>
+        <v>2.218</v>
       </c>
       <c r="K6" t="n">
-        <v>58</v>
+        <v>114</v>
       </c>
       <c r="L6" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M6" t="n">
-        <v>2.1885</v>
+        <v>2.4374</v>
       </c>
       <c r="N6" t="n">
-        <v>143</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7">
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.0751</v>
+        <v>2.3946</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3828</v>
+        <v>0.443</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0751</v>
+        <v>2.3946</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4813</v>
+        <v>2.6828</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4062</v>
+        <v>-0.2882</v>
       </c>
       <c r="H7" t="n">
-        <v>2.4813</v>
+        <v>3.9663</v>
       </c>
       <c r="I7" t="n">
-        <v>2.0112</v>
+        <v>2.0623</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.4062</v>
+        <v>-0.2882</v>
       </c>
       <c r="K7" t="n">
         <v>132</v>
@@ -759,7 +759,7 @@
         <v>56</v>
       </c>
       <c r="M7" t="n">
-        <v>1.605</v>
+        <v>1.7741</v>
       </c>
       <c r="N7" t="n">
         <v>188</v>
@@ -768,323 +768,323 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>Hiko</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9856</v>
+        <v>0.8686</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0512</v>
+        <v>-0.2459</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9856</v>
+        <v>0.8686</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1565</v>
+        <v>0.9493</v>
       </c>
       <c r="G8" t="n">
-        <v>2.1421</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1565</v>
+        <v>0.9493</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9374</v>
+        <v>0.4936</v>
       </c>
       <c r="J8" t="n">
-        <v>2.1421</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="L8" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="M8" t="n">
-        <v>1.2047</v>
+        <v>0.4129</v>
       </c>
       <c r="N8" t="n">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Hiko</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2965</v>
+        <v>0.5566</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3258</v>
+        <v>-0.3867</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2965</v>
+        <v>0.5566</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4639</v>
+        <v>0.3687</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1674</v>
+        <v>0.1879</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4639</v>
+        <v>0.3687</v>
       </c>
       <c r="I9" t="n">
-        <v>0.376</v>
+        <v>0.1917</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1674</v>
+        <v>0.1879</v>
       </c>
       <c r="K9" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="L9" t="n">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2086</v>
+        <v>0.3796</v>
       </c>
       <c r="N9" t="n">
-        <v>131</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0576</v>
+        <v>0.4544</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.421</v>
+        <v>-0.4329</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0576</v>
+        <v>0.4544</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1467</v>
+        <v>-1.5649</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0891</v>
+        <v>2.0193</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1467</v>
+        <v>-1.5649</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1189</v>
+        <v>-0.8137</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0891</v>
+        <v>2.0193</v>
       </c>
       <c r="K10" t="n">
-        <v>114</v>
+        <v>58</v>
       </c>
       <c r="L10" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M10" t="n">
-        <v>0.02980000000000001</v>
+        <v>1.2056</v>
       </c>
       <c r="N10" t="n">
-        <v>198</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.5547</v>
+        <v>0.4517</v>
       </c>
       <c r="C11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.6649</v>
+        <v>-0.4341</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5547</v>
+        <v>0.4517</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3066</v>
+        <v>0.9941</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2481</v>
+        <v>-0.5424</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3066</v>
+        <v>0.9941</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2485</v>
+        <v>0.5169</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2481</v>
+        <v>-0.5424</v>
       </c>
       <c r="K11" t="n">
-        <v>76</v>
+        <v>132</v>
       </c>
       <c r="L11" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4966</v>
+        <v>-0.02549999999999997</v>
       </c>
       <c r="N11" t="n">
-        <v>131</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.6175</v>
+        <v>0.2419</v>
       </c>
       <c r="C12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.6899</v>
+        <v>-0.5288</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.6175</v>
+        <v>0.2419</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0848</v>
+        <v>1.679</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.5327</v>
+        <v>-1.4371</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.0848</v>
+        <v>1.679</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0687</v>
+        <v>0.873</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5327</v>
+        <v>-1.4371</v>
       </c>
       <c r="K12" t="n">
-        <v>58</v>
+        <v>114</v>
       </c>
       <c r="L12" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.6013999999999999</v>
+        <v>-0.5641</v>
       </c>
       <c r="N12" t="n">
-        <v>143</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.631</v>
+        <v>-0.1958</v>
       </c>
       <c r="C13" t="n">
         <v>-0</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.6953</v>
+        <v>-0.7264</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.631</v>
+        <v>-0.1958</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1865</v>
+        <v>-0.1081</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.8175</v>
+        <v>-0.0877</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1865</v>
+        <v>-0.1081</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1512</v>
+        <v>-0.0562</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.8175</v>
+        <v>-0.0877</v>
       </c>
       <c r="K13" t="n">
-        <v>132</v>
+        <v>76</v>
       </c>
       <c r="L13" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.6663</v>
+        <v>-0.1439</v>
       </c>
       <c r="N13" t="n">
-        <v>188</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.917</v>
+        <v>-0.6761</v>
       </c>
       <c r="C14" t="n">
         <v>-0</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.8092</v>
+        <v>-0.9432</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.917</v>
+        <v>-0.6761</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8401999999999999</v>
+        <v>0.0412</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.7572</v>
+        <v>-0.7173</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8401999999999999</v>
+        <v>0.0412</v>
       </c>
       <c r="I14" t="n">
-        <v>0.681</v>
+        <v>0.0214</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.7572</v>
+        <v>-0.7173</v>
       </c>
       <c r="K14" t="n">
-        <v>114</v>
+        <v>58</v>
       </c>
       <c r="L14" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.0762</v>
+        <v>-0.6959000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>198</v>
+        <v>143</v>
       </c>
     </row>
     <row r="15">
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-1.0214</v>
+        <v>-1.0309</v>
       </c>
       <c r="C15" t="n">
         <v>-0</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.8508</v>
+        <v>-1.1034</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.0214</v>
+        <v>-1.0309</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9448</v>
+        <v>-0.9378</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0766</v>
+        <v>-0.0931</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.9448</v>
+        <v>-0.9378</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7658</v>
+        <v>-0.4876</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.0766</v>
+        <v>-0.0931</v>
       </c>
       <c r="K15" t="n">
         <v>76</v>
@@ -1127,7 +1127,7 @@
         <v>55</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8424</v>
+        <v>-0.5807</v>
       </c>
       <c r="N15" t="n">
         <v>131</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-1.2284</v>
+        <v>-1.0596</v>
       </c>
       <c r="C16" t="n">
         <v>-0</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.9333</v>
+        <v>-1.1164</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.2284</v>
+        <v>-1.0596</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0547</v>
+        <v>-0.9076</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1737</v>
+        <v>-0.152</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.0547</v>
+        <v>-0.9076</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8549</v>
+        <v>-0.4719</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1737</v>
+        <v>-0.152</v>
       </c>
       <c r="K16" t="n">
         <v>132</v>
@@ -1173,7 +1173,7 @@
         <v>56</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0286</v>
+        <v>-0.6239</v>
       </c>
       <c r="N16" t="n">
         <v>188</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-1.2652</v>
+        <v>-1.2548</v>
       </c>
       <c r="C17" t="n">
         <v>-0</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.948</v>
+        <v>-1.2045</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.2652</v>
+        <v>-1.2548</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4418</v>
+        <v>-0.4466</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8234</v>
+        <v>-0.8082</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4418</v>
+        <v>-0.4466</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3581</v>
+        <v>-0.2322</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.8234</v>
+        <v>-0.8082</v>
       </c>
       <c r="K17" t="n">
         <v>58</v>
@@ -1219,7 +1219,7 @@
         <v>85</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1815</v>
+        <v>-1.0404</v>
       </c>
       <c r="N17" t="n">
         <v>143</v>
@@ -1228,35 +1228,35 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>adreN</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-1.7013</v>
+        <v>-1.2697</v>
       </c>
       <c r="C18" t="n">
         <v>-0</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1217</v>
+        <v>-1.2112</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.7013</v>
+        <v>-1.2697</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9161</v>
+        <v>-0.6556</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7852</v>
+        <v>-0.6141</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.9161</v>
+        <v>-0.6556</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7425</v>
+        <v>-0.3409</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7852</v>
+        <v>-0.6141</v>
       </c>
       <c r="K18" t="n">
         <v>76</v>
@@ -1265,7 +1265,7 @@
         <v>55</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.5277</v>
+        <v>-0.955</v>
       </c>
       <c r="N18" t="n">
         <v>131</v>
@@ -1274,35 +1274,35 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>adreN</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-1.7677</v>
+        <v>-1.2701</v>
       </c>
       <c r="C19" t="n">
         <v>-0</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1482</v>
+        <v>-1.2114</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7677</v>
+        <v>-1.2701</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.843</v>
+        <v>-0.7572</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.9247</v>
+        <v>-0.5129</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.843</v>
+        <v>-0.7572</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6833</v>
+        <v>-0.3937</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.9247</v>
+        <v>-0.5129</v>
       </c>
       <c r="K19" t="n">
         <v>76</v>
@@ -1311,7 +1311,7 @@
         <v>55</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.608</v>
+        <v>-0.9066000000000001</v>
       </c>
       <c r="N19" t="n">
         <v>131</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-1.9647</v>
+        <v>-1.3402</v>
       </c>
       <c r="C20" t="n">
         <v>-0</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2266</v>
+        <v>-1.243</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9647</v>
+        <v>-1.3402</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5374</v>
+        <v>-0.2769</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.4273</v>
+        <v>-1.0633</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5374</v>
+        <v>-0.2769</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4356</v>
+        <v>-0.144</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.4273</v>
+        <v>-1.0633</v>
       </c>
       <c r="K20" t="n">
         <v>114</v>
@@ -1357,7 +1357,7 @@
         <v>84</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8629</v>
+        <v>-1.2073</v>
       </c>
       <c r="N20" t="n">
         <v>198</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-3.4277</v>
+        <v>-3.3467</v>
       </c>
       <c r="C21" t="n">
         <v>-0</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8095</v>
+        <v>-2.1489</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.4277</v>
+        <v>-3.3467</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.4277</v>
+        <v>-2.6802</v>
       </c>
       <c r="G21" t="n">
-        <v>-1</v>
+        <v>-0.6665</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.4277</v>
+        <v>-2.6802</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.9677</v>
+        <v>-1.3936</v>
       </c>
       <c r="J21" t="n">
-        <v>-1</v>
+        <v>-0.6665</v>
       </c>
       <c r="K21" t="n">
         <v>132</v>
@@ -1403,7 +1403,7 @@
         <v>56</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.9677</v>
+        <v>-2.0601</v>
       </c>
       <c r="N21" t="n">
         <v>188</v>
@@ -1509,10 +1509,10 @@
         <v>1.34</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9079</v>
+        <v>0.8995</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9079</v>
+        <v>0.8995</v>
       </c>
     </row>
     <row r="3">
@@ -1549,10 +1549,10 @@
         <v>1.27</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7464</v>
+        <v>0.7363</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7464</v>
+        <v>0.7363</v>
       </c>
     </row>
     <row r="4">
@@ -1589,10 +1589,10 @@
         <v>1.26</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7223000000000001</v>
+        <v>0.7125</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7223000000000001</v>
+        <v>0.7125</v>
       </c>
     </row>
     <row r="5">
@@ -1629,10 +1629,10 @@
         <v>1.17</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4844</v>
+        <v>0.4942</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4844</v>
+        <v>0.4942</v>
       </c>
     </row>
     <row r="6">
@@ -1669,10 +1669,10 @@
         <v>0.74</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8577</v>
+        <v>-0.8163</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.8577</v>
+        <v>-0.8163</v>
       </c>
     </row>
     <row r="7">
@@ -1709,10 +1709,10 @@
         <v>1.18</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3913</v>
+        <v>0.4393</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3913</v>
+        <v>0.4393</v>
       </c>
     </row>
     <row r="8">
@@ -1749,10 +1749,10 @@
         <v>0.88</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2208</v>
+        <v>-0.145</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2208</v>
+        <v>-0.145</v>
       </c>
     </row>
     <row r="9">
@@ -1789,10 +1789,10 @@
         <v>0.87</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2395</v>
+        <v>-0.1555</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2395</v>
+        <v>-0.1555</v>
       </c>
     </row>
     <row r="10">
@@ -1829,10 +1829,10 @@
         <v>0.87</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2395</v>
+        <v>-0.1555</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2395</v>
+        <v>-0.1555</v>
       </c>
     </row>
     <row r="11">
@@ -1869,10 +1869,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5123</v>
+        <v>-0.3334</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5123</v>
+        <v>-0.3334</v>
       </c>
     </row>
     <row r="12">
@@ -1909,10 +1909,10 @@
         <v>1.4</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1065</v>
+        <v>1.0571</v>
       </c>
       <c r="J12" t="n">
-        <v>30.982</v>
+        <v>29.5988</v>
       </c>
     </row>
     <row r="13">
@@ -1949,10 +1949,10 @@
         <v>1.12</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4348</v>
+        <v>0.3952</v>
       </c>
       <c r="J13" t="n">
-        <v>12.1744</v>
+        <v>11.0656</v>
       </c>
     </row>
     <row r="14">
@@ -1989,10 +1989,10 @@
         <v>0.92</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3521</v>
+        <v>-0.2986</v>
       </c>
       <c r="J14" t="n">
-        <v>-9.8588</v>
+        <v>-8.360799999999999</v>
       </c>
     </row>
     <row r="15">
@@ -2029,10 +2029,10 @@
         <v>0.86</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5242</v>
+        <v>-0.47</v>
       </c>
       <c r="J15" t="n">
-        <v>-14.6776</v>
+        <v>-13.16</v>
       </c>
     </row>
     <row r="16">
@@ -2069,10 +2069,10 @@
         <v>0.85</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.551</v>
+        <v>-0.4973</v>
       </c>
       <c r="J16" t="n">
-        <v>-15.428</v>
+        <v>-13.9244</v>
       </c>
     </row>
     <row r="17">
@@ -2109,10 +2109,10 @@
         <v>1.37</v>
       </c>
       <c r="I17" t="n">
-        <v>0.627</v>
+        <v>0.7611</v>
       </c>
       <c r="J17" t="n">
-        <v>17.556</v>
+        <v>21.3108</v>
       </c>
     </row>
     <row r="18">
@@ -2149,10 +2149,10 @@
         <v>1.2</v>
       </c>
       <c r="I18" t="n">
-        <v>0.402</v>
+        <v>0.4569</v>
       </c>
       <c r="J18" t="n">
-        <v>11.256</v>
+        <v>12.7932</v>
       </c>
     </row>
     <row r="19">
@@ -2189,10 +2189,10 @@
         <v>1.08</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2132</v>
+        <v>0.2186</v>
       </c>
       <c r="J19" t="n">
-        <v>5.9696</v>
+        <v>6.1208</v>
       </c>
     </row>
     <row r="20">
@@ -2229,10 +2229,10 @@
         <v>0.68</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5364</v>
+        <v>-0.3491</v>
       </c>
       <c r="J20" t="n">
-        <v>-15.0192</v>
+        <v>-9.774800000000001</v>
       </c>
     </row>
     <row r="21">
@@ -2269,10 +2269,10 @@
         <v>0.41</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8601</v>
+        <v>-0.5945</v>
       </c>
       <c r="J21" t="n">
-        <v>-24.0828</v>
+        <v>-16.646</v>
       </c>
     </row>
     <row r="22">
@@ -2309,10 +2309,10 @@
         <v>1.07</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2409</v>
+        <v>0.239</v>
       </c>
       <c r="J22" t="n">
-        <v>6.7452</v>
+        <v>6.692</v>
       </c>
     </row>
     <row r="23">
@@ -2349,10 +2349,10 @@
         <v>1.02</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1408</v>
+        <v>0.1137</v>
       </c>
       <c r="J23" t="n">
-        <v>3.9424</v>
+        <v>3.1836</v>
       </c>
     </row>
     <row r="24">
@@ -2389,10 +2389,10 @@
         <v>0.89</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1544</v>
+        <v>-0.1278</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.3232</v>
+        <v>-3.5784</v>
       </c>
     </row>
     <row r="25">
@@ -2429,10 +2429,10 @@
         <v>0.8</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3275</v>
+        <v>-0.2186</v>
       </c>
       <c r="J25" t="n">
-        <v>-9.17</v>
+        <v>-6.1208</v>
       </c>
     </row>
     <row r="26">
@@ -2469,10 +2469,10 @@
         <v>0.38</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.8813</v>
+        <v>-0.6104000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>-24.6764</v>
+        <v>-17.0912</v>
       </c>
     </row>
     <row r="27">
@@ -2509,10 +2509,10 @@
         <v>1.35</v>
       </c>
       <c r="I27" t="n">
-        <v>0.9161</v>
+        <v>0.913</v>
       </c>
       <c r="J27" t="n">
-        <v>25.6508</v>
+        <v>25.564</v>
       </c>
     </row>
     <row r="28">
@@ -2549,10 +2549,10 @@
         <v>1.32</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8485</v>
+        <v>0.8449</v>
       </c>
       <c r="J28" t="n">
-        <v>23.758</v>
+        <v>23.6572</v>
       </c>
     </row>
     <row r="29">
@@ -2589,10 +2589,10 @@
         <v>1.22</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6042</v>
+        <v>0.6105</v>
       </c>
       <c r="J29" t="n">
-        <v>16.9176</v>
+        <v>17.094</v>
       </c>
     </row>
     <row r="30">
@@ -2629,10 +2629,10 @@
         <v>1.2</v>
       </c>
       <c r="I30" t="n">
-        <v>0.5489000000000001</v>
+        <v>0.5627</v>
       </c>
       <c r="J30" t="n">
-        <v>15.3692</v>
+        <v>15.7556</v>
       </c>
     </row>
     <row r="31">
@@ -2669,10 +2669,10 @@
         <v>0.82</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6774</v>
+        <v>-0.6187</v>
       </c>
       <c r="J31" t="n">
-        <v>-18.9672</v>
+        <v>-17.3236</v>
       </c>
     </row>
     <row r="32">
@@ -2709,10 +2709,10 @@
         <v>1.44</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6905</v>
+        <v>0.8499</v>
       </c>
       <c r="J32" t="n">
-        <v>19.334</v>
+        <v>23.7972</v>
       </c>
     </row>
     <row r="33">
@@ -2749,10 +2749,10 @@
         <v>1.26</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4638</v>
+        <v>0.5434</v>
       </c>
       <c r="J33" t="n">
-        <v>12.9864</v>
+        <v>15.2152</v>
       </c>
     </row>
     <row r="34">
@@ -2789,10 +2789,10 @@
         <v>1.05</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1308</v>
+        <v>0.1374</v>
       </c>
       <c r="J34" t="n">
-        <v>3.6624</v>
+        <v>3.8472</v>
       </c>
     </row>
     <row r="35">
@@ -2829,10 +2829,10 @@
         <v>0.92</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1961</v>
+        <v>-0.1127</v>
       </c>
       <c r="J35" t="n">
-        <v>-5.4908</v>
+        <v>-3.1556</v>
       </c>
     </row>
     <row r="36">
@@ -2869,10 +2869,10 @@
         <v>0.38</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8986</v>
+        <v>-0.6256</v>
       </c>
       <c r="J36" t="n">
-        <v>-25.1608</v>
+        <v>-17.5168</v>
       </c>
     </row>
     <row r="37">
@@ -2909,10 +2909,10 @@
         <v>1.33</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9736</v>
+        <v>0.9458</v>
       </c>
       <c r="J37" t="n">
-        <v>27.2608</v>
+        <v>26.4824</v>
       </c>
     </row>
     <row r="38">
@@ -2949,10 +2949,10 @@
         <v>1.18</v>
       </c>
       <c r="I38" t="n">
-        <v>0.6179</v>
+        <v>0.5696</v>
       </c>
       <c r="J38" t="n">
-        <v>17.3012</v>
+        <v>15.9488</v>
       </c>
     </row>
     <row r="39">
@@ -2989,10 +2989,10 @@
         <v>0.92</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.3341</v>
+        <v>-0.2896</v>
       </c>
       <c r="J39" t="n">
-        <v>-9.354799999999999</v>
+        <v>-8.1088</v>
       </c>
     </row>
     <row r="40">
@@ -3029,10 +3029,10 @@
         <v>0.8</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.6666</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>-18.6648</v>
+        <v>-17.374</v>
       </c>
     </row>
     <row r="41">
@@ -3069,10 +3069,10 @@
         <v>0.76</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.7647</v>
+        <v>-0.7233000000000001</v>
       </c>
       <c r="J41" t="n">
-        <v>-21.4116</v>
+        <v>-20.2524</v>
       </c>
     </row>
     <row r="42">
@@ -3109,10 +3109,10 @@
         <v>1.34</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5797</v>
+        <v>0.6963</v>
       </c>
       <c r="J42" t="n">
-        <v>16.2316</v>
+        <v>19.4964</v>
       </c>
     </row>
     <row r="43">
@@ -3149,10 +3149,10 @@
         <v>1.05</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1458</v>
+        <v>0.1445</v>
       </c>
       <c r="J43" t="n">
-        <v>4.0824</v>
+        <v>4.046</v>
       </c>
     </row>
     <row r="44">
@@ -3189,10 +3189,10 @@
         <v>0.98</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.0477</v>
+        <v>-0.0344</v>
       </c>
       <c r="J44" t="n">
-        <v>-1.3356</v>
+        <v>-0.9631999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -3229,10 +3229,10 @@
         <v>0.91</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2021</v>
+        <v>-0.1204</v>
       </c>
       <c r="J45" t="n">
-        <v>-5.6588</v>
+        <v>-3.3712</v>
       </c>
     </row>
     <row r="46">
@@ -3269,10 +3269,10 @@
         <v>0.6</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6423</v>
+        <v>-0.4267</v>
       </c>
       <c r="J46" t="n">
-        <v>-17.9844</v>
+        <v>-11.9476</v>
       </c>
     </row>
     <row r="47">
@@ -3309,10 +3309,10 @@
         <v>1.48</v>
       </c>
       <c r="I47" t="n">
-        <v>1.2353</v>
+        <v>1.1443</v>
       </c>
       <c r="J47" t="n">
-        <v>34.5884</v>
+        <v>32.0404</v>
       </c>
     </row>
     <row r="48">
@@ -3349,10 +3349,10 @@
         <v>1.36</v>
       </c>
       <c r="I48" t="n">
-        <v>0.9843</v>
+        <v>0.9651</v>
       </c>
       <c r="J48" t="n">
-        <v>27.5604</v>
+        <v>27.0228</v>
       </c>
     </row>
     <row r="49">
@@ -3389,10 +3389,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.3211</v>
+        <v>-0.2553</v>
       </c>
       <c r="J49" t="n">
-        <v>-8.9908</v>
+        <v>-7.1484</v>
       </c>
     </row>
     <row r="50">
@@ -3429,10 +3429,10 @@
         <v>0.9</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.4408</v>
+        <v>-0.3761</v>
       </c>
       <c r="J50" t="n">
-        <v>-12.3424</v>
+        <v>-10.5308</v>
       </c>
     </row>
     <row r="51">
@@ -3469,10 +3469,10 @@
         <v>0.8</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.7014</v>
+        <v>-0.6487000000000001</v>
       </c>
       <c r="J51" t="n">
-        <v>-19.6392</v>
+        <v>-18.1636</v>
       </c>
     </row>
     <row r="52">
@@ -3509,10 +3509,10 @@
         <v>1.07</v>
       </c>
       <c r="I52" t="n">
-        <v>0.2376</v>
+        <v>0.2355</v>
       </c>
       <c r="J52" t="n">
-        <v>7.128</v>
+        <v>7.065</v>
       </c>
     </row>
     <row r="53">
@@ -3549,10 +3549,10 @@
         <v>0.92</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1035</v>
+        <v>-0.0948</v>
       </c>
       <c r="J53" t="n">
-        <v>-3.105</v>
+        <v>-2.844</v>
       </c>
     </row>
     <row r="54">
@@ -3589,10 +3589,10 @@
         <v>0.87</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1949</v>
+        <v>-0.1504</v>
       </c>
       <c r="J54" t="n">
-        <v>-5.847</v>
+        <v>-4.512</v>
       </c>
     </row>
     <row r="55">
@@ -3629,10 +3629,10 @@
         <v>0.7</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.483</v>
+        <v>-0.3161</v>
       </c>
       <c r="J55" t="n">
-        <v>-14.49</v>
+        <v>-9.483000000000001</v>
       </c>
     </row>
     <row r="56">
@@ -3669,10 +3669,10 @@
         <v>0.64</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.5649</v>
+        <v>-0.3729</v>
       </c>
       <c r="J56" t="n">
-        <v>-16.947</v>
+        <v>-11.187</v>
       </c>
     </row>
     <row r="57">
@@ -3709,10 +3709,10 @@
         <v>1.34</v>
       </c>
       <c r="I57" t="n">
-        <v>0.9198</v>
+        <v>0.9075</v>
       </c>
       <c r="J57" t="n">
-        <v>27.594</v>
+        <v>27.225</v>
       </c>
     </row>
     <row r="58">
@@ -3749,10 +3749,10 @@
         <v>1.22</v>
       </c>
       <c r="I58" t="n">
-        <v>0.6364</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="J58" t="n">
-        <v>19.092</v>
+        <v>18.675</v>
       </c>
     </row>
     <row r="59">
@@ -3789,10 +3789,10 @@
         <v>1.13</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3721</v>
+        <v>0.3975</v>
       </c>
       <c r="J59" t="n">
-        <v>11.163</v>
+        <v>11.925</v>
       </c>
     </row>
     <row r="60">
@@ -3829,10 +3829,10 @@
         <v>1.01</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.037</v>
+        <v>0.0231</v>
       </c>
       <c r="J60" t="n">
-        <v>-1.11</v>
+        <v>0.6929999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -3869,10 +3869,10 @@
         <v>0.97</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.236</v>
+        <v>-0.165</v>
       </c>
       <c r="J61" t="n">
-        <v>-7.08</v>
+        <v>-4.95</v>
       </c>
     </row>
     <row r="62">
@@ -3909,10 +3909,10 @@
         <v>1.17</v>
       </c>
       <c r="I62" t="n">
-        <v>0.412</v>
+        <v>0.4649</v>
       </c>
       <c r="J62" t="n">
-        <v>10.3</v>
+        <v>11.6225</v>
       </c>
     </row>
     <row r="63">
@@ -3949,10 +3949,10 @@
         <v>1.08</v>
       </c>
       <c r="I63" t="n">
-        <v>0.2684</v>
+        <v>0.2733</v>
       </c>
       <c r="J63" t="n">
-        <v>6.71</v>
+        <v>6.8325</v>
       </c>
     </row>
     <row r="64">
@@ -3989,10 +3989,10 @@
         <v>0.83</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.2484</v>
+        <v>-0.1875</v>
       </c>
       <c r="J64" t="n">
-        <v>-6.21</v>
+        <v>-4.6875</v>
       </c>
     </row>
     <row r="65">
@@ -4029,10 +4029,10 @@
         <v>0.51</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.7238</v>
+        <v>-0.4893</v>
       </c>
       <c r="J65" t="n">
-        <v>-18.095</v>
+        <v>-12.2325</v>
       </c>
     </row>
     <row r="66">
@@ -4069,10 +4069,10 @@
         <v>0.45</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.7964</v>
+        <v>-0.5443</v>
       </c>
       <c r="J66" t="n">
-        <v>-19.91</v>
+        <v>-13.6075</v>
       </c>
     </row>
     <row r="67">
@@ -4109,10 +4109,10 @@
         <v>1.45</v>
       </c>
       <c r="I67" t="n">
-        <v>1.1398</v>
+        <v>1.0861</v>
       </c>
       <c r="J67" t="n">
-        <v>28.495</v>
+        <v>27.1525</v>
       </c>
     </row>
     <row r="68">
@@ -4149,10 +4149,10 @@
         <v>1.38</v>
       </c>
       <c r="I68" t="n">
-        <v>0.9923999999999999</v>
+        <v>0.9809</v>
       </c>
       <c r="J68" t="n">
-        <v>24.81</v>
+        <v>24.5225</v>
       </c>
     </row>
     <row r="69">
@@ -4189,10 +4189,10 @@
         <v>1.14</v>
       </c>
       <c r="I69" t="n">
-        <v>0.376</v>
+        <v>0.4188</v>
       </c>
       <c r="J69" t="n">
-        <v>9.4</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="70">
@@ -4229,10 +4229,10 @@
         <v>1.03</v>
       </c>
       <c r="I70" t="n">
-        <v>0.031</v>
+        <v>0.094</v>
       </c>
       <c r="J70" t="n">
-        <v>0.775</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="71">
@@ -4269,10 +4269,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6963</v>
+        <v>-0.6399</v>
       </c>
       <c r="J71" t="n">
-        <v>-17.4075</v>
+        <v>-15.9975</v>
       </c>
     </row>
     <row r="72">
@@ -4309,10 +4309,10 @@
         <v>1.48</v>
       </c>
       <c r="I72" t="n">
-        <v>0.7039</v>
+        <v>0.6208</v>
       </c>
       <c r="J72" t="n">
-        <v>19.7092</v>
+        <v>17.3824</v>
       </c>
     </row>
     <row r="73">
@@ -4349,10 +4349,10 @@
         <v>1.21</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3576</v>
+        <v>0.3033</v>
       </c>
       <c r="J73" t="n">
-        <v>10.0128</v>
+        <v>8.4924</v>
       </c>
     </row>
     <row r="74">
@@ -4389,10 +4389,10 @@
         <v>1.1</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1667</v>
+        <v>0.1613</v>
       </c>
       <c r="J74" t="n">
-        <v>4.6676</v>
+        <v>4.5164</v>
       </c>
     </row>
     <row r="75">
@@ -4429,10 +4429,10 @@
         <v>0.93</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2072</v>
+        <v>-0.1124</v>
       </c>
       <c r="J75" t="n">
-        <v>-5.8016</v>
+        <v>-3.1472</v>
       </c>
     </row>
     <row r="76">
@@ -4469,10 +4469,10 @@
         <v>0.86</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3201</v>
+        <v>-0.1902</v>
       </c>
       <c r="J76" t="n">
-        <v>-8.9628</v>
+        <v>-5.3256</v>
       </c>
     </row>
     <row r="77">
@@ -4509,10 +4509,10 @@
         <v>1.17</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4062</v>
+        <v>0.3497</v>
       </c>
       <c r="J77" t="n">
-        <v>11.3736</v>
+        <v>9.791600000000001</v>
       </c>
     </row>
     <row r="78">
@@ -4549,10 +4549,10 @@
         <v>0.89</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.1494</v>
+        <v>-0.1263</v>
       </c>
       <c r="J78" t="n">
-        <v>-4.1832</v>
+        <v>-3.5364</v>
       </c>
     </row>
     <row r="79">
@@ -4589,10 +4589,10 @@
         <v>0.83</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2584</v>
+        <v>-0.1889</v>
       </c>
       <c r="J79" t="n">
-        <v>-7.2352</v>
+        <v>-5.2892</v>
       </c>
     </row>
     <row r="80">
@@ -4629,10 +4629,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.4915</v>
+        <v>-0.3231</v>
       </c>
       <c r="J80" t="n">
-        <v>-13.762</v>
+        <v>-9.046799999999999</v>
       </c>
     </row>
     <row r="81">
@@ -4669,10 +4669,10 @@
         <v>0.53</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.7018</v>
+        <v>-0.4727</v>
       </c>
       <c r="J81" t="n">
-        <v>-19.6504</v>
+        <v>-13.2356</v>
       </c>
     </row>
     <row r="82">
@@ -4709,10 +4709,10 @@
         <v>1.06</v>
       </c>
       <c r="I82" t="n">
-        <v>0.2611</v>
+        <v>0.263</v>
       </c>
       <c r="J82" t="n">
-        <v>6.0053</v>
+        <v>6.049</v>
       </c>
     </row>
     <row r="83">
@@ -4749,10 +4749,10 @@
         <v>0.82</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.2286</v>
+        <v>-0.1877</v>
       </c>
       <c r="J83" t="n">
-        <v>-5.2578</v>
+        <v>-4.3171</v>
       </c>
     </row>
     <row r="84">
@@ -4789,10 +4789,10 @@
         <v>0.73</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.3936</v>
+        <v>-0.2746</v>
       </c>
       <c r="J84" t="n">
-        <v>-9.0528</v>
+        <v>-6.3158</v>
       </c>
     </row>
     <row r="85">
@@ -4829,10 +4829,10 @@
         <v>0.57</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.6316000000000001</v>
+        <v>-0.424</v>
       </c>
       <c r="J85" t="n">
-        <v>-14.5268</v>
+        <v>-9.752000000000001</v>
       </c>
     </row>
     <row r="86">
@@ -4869,10 +4869,10 @@
         <v>0.53</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.6841</v>
+        <v>-0.4614</v>
       </c>
       <c r="J86" t="n">
-        <v>-15.7343</v>
+        <v>-10.6122</v>
       </c>
     </row>
     <row r="87">
@@ -4909,10 +4909,10 @@
         <v>1.26</v>
       </c>
       <c r="I87" t="n">
-        <v>0.7399</v>
+        <v>0.7219</v>
       </c>
       <c r="J87" t="n">
-        <v>17.0177</v>
+        <v>16.6037</v>
       </c>
     </row>
     <row r="88">
@@ -4949,10 +4949,10 @@
         <v>1.24</v>
       </c>
       <c r="I88" t="n">
-        <v>0.6913</v>
+        <v>0.6736</v>
       </c>
       <c r="J88" t="n">
-        <v>15.8999</v>
+        <v>15.4928</v>
       </c>
     </row>
     <row r="89">
@@ -4989,10 +4989,10 @@
         <v>1.19</v>
       </c>
       <c r="I89" t="n">
-        <v>0.5636</v>
+        <v>0.5506</v>
       </c>
       <c r="J89" t="n">
-        <v>12.9628</v>
+        <v>12.6638</v>
       </c>
     </row>
     <row r="90">
@@ -5029,10 +5029,10 @@
         <v>1.06</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1529</v>
+        <v>0.2021</v>
       </c>
       <c r="J90" t="n">
-        <v>3.5167</v>
+        <v>4.6483</v>
       </c>
     </row>
     <row r="91">
@@ -5069,10 +5069,10 @@
         <v>0.88</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5072</v>
+        <v>-0.4414</v>
       </c>
       <c r="J91" t="n">
-        <v>-11.6656</v>
+        <v>-10.1522</v>
       </c>
     </row>
     <row r="92">
@@ -5109,10 +5109,10 @@
         <v>1.24</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4703</v>
+        <v>0.4587</v>
       </c>
       <c r="J92" t="n">
-        <v>14.109</v>
+        <v>13.761</v>
       </c>
     </row>
     <row r="93">
@@ -5149,10 +5149,10 @@
         <v>1</v>
       </c>
       <c r="I93" t="n">
-        <v>0.047</v>
+        <v>0.0169</v>
       </c>
       <c r="J93" t="n">
-        <v>1.41</v>
+        <v>0.507</v>
       </c>
     </row>
     <row r="94">
@@ -5189,10 +5189,10 @@
         <v>0.9</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1915</v>
+        <v>-0.1253</v>
       </c>
       <c r="J94" t="n">
-        <v>-5.745</v>
+        <v>-3.759</v>
       </c>
     </row>
     <row r="95">
@@ -5229,10 +5229,10 @@
         <v>0.82</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3296</v>
+        <v>-0.2085</v>
       </c>
       <c r="J95" t="n">
-        <v>-9.888</v>
+        <v>-6.255</v>
       </c>
     </row>
     <row r="96">
@@ -5269,10 +5269,10 @@
         <v>0.61</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.6195000000000001</v>
+        <v>-0.4104</v>
       </c>
       <c r="J96" t="n">
-        <v>-18.585</v>
+        <v>-12.312</v>
       </c>
     </row>
     <row r="97">
@@ -5309,10 +5309,10 @@
         <v>1.37</v>
       </c>
       <c r="I97" t="n">
-        <v>1.0811</v>
+        <v>0.7655999999999999</v>
       </c>
       <c r="J97" t="n">
-        <v>32.433</v>
+        <v>22.968</v>
       </c>
     </row>
     <row r="98">
@@ -5349,10 +5349,10 @@
         <v>1.09</v>
       </c>
       <c r="I98" t="n">
-        <v>0.3907</v>
+        <v>0.3299</v>
       </c>
       <c r="J98" t="n">
-        <v>11.721</v>
+        <v>9.897</v>
       </c>
     </row>
     <row r="99">
@@ -5389,10 +5389,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2424</v>
+        <v>-0.2199</v>
       </c>
       <c r="J99" t="n">
-        <v>-7.272</v>
+        <v>-6.597</v>
       </c>
     </row>
     <row r="100">
@@ -5429,10 +5429,10 @@
         <v>0.93</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2776</v>
+        <v>-0.2505</v>
       </c>
       <c r="J100" t="n">
-        <v>-8.327999999999999</v>
+        <v>-7.515</v>
       </c>
     </row>
     <row r="101">
@@ -5469,10 +5469,10 @@
         <v>0.49</v>
       </c>
       <c r="I101" t="n">
-        <v>-1.3417</v>
+        <v>-1.3642</v>
       </c>
       <c r="J101" t="n">
-        <v>-40.251</v>
+        <v>-40.926</v>
       </c>
     </row>
     <row r="102">
@@ -5509,10 +5509,10 @@
         <v>0.98</v>
       </c>
       <c r="I102" t="n">
-        <v>0.0259</v>
+        <v>-0.0123</v>
       </c>
       <c r="J102" t="n">
-        <v>0.6734</v>
+        <v>-0.3198</v>
       </c>
     </row>
     <row r="103">
@@ -5549,10 +5549,10 @@
         <v>0.93</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.0766</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="J103" t="n">
-        <v>-1.9916</v>
+        <v>-2.0722</v>
       </c>
     </row>
     <row r="104">
@@ -5589,10 +5589,10 @@
         <v>0.85</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.2207</v>
+        <v>-0.1689</v>
       </c>
       <c r="J104" t="n">
-        <v>-5.7382</v>
+        <v>-4.3914</v>
       </c>
     </row>
     <row r="105">
@@ -5629,10 +5629,10 @@
         <v>0.76</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3879</v>
+        <v>-0.2561</v>
       </c>
       <c r="J105" t="n">
-        <v>-10.0854</v>
+        <v>-6.6586</v>
       </c>
     </row>
     <row r="106">
@@ -5669,10 +5669,10 @@
         <v>0.59</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.626</v>
+        <v>-0.4171</v>
       </c>
       <c r="J106" t="n">
-        <v>-16.276</v>
+        <v>-10.8446</v>
       </c>
     </row>
     <row r="107">
@@ -5709,10 +5709,10 @@
         <v>1.62</v>
       </c>
       <c r="I107" t="n">
-        <v>1.4679</v>
+        <v>1.0272</v>
       </c>
       <c r="J107" t="n">
-        <v>38.1654</v>
+        <v>26.7072</v>
       </c>
     </row>
     <row r="108">
@@ -5749,10 +5749,10 @@
         <v>1.33</v>
       </c>
       <c r="I108" t="n">
-        <v>0.8756</v>
+        <v>0.65</v>
       </c>
       <c r="J108" t="n">
-        <v>22.7656</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="109">
@@ -5789,10 +5789,10 @@
         <v>1.2</v>
       </c>
       <c r="I109" t="n">
-        <v>0.5557</v>
+        <v>0.4696</v>
       </c>
       <c r="J109" t="n">
-        <v>14.4482</v>
+        <v>12.2096</v>
       </c>
     </row>
     <row r="110">
@@ -5829,10 +5829,10 @@
         <v>0.98</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2141</v>
+        <v>-0.1381</v>
       </c>
       <c r="J110" t="n">
-        <v>-5.5666</v>
+        <v>-3.5906</v>
       </c>
     </row>
     <row r="111">
@@ -5869,10 +5869,10 @@
         <v>0.74</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.8618</v>
+        <v>-0.8206</v>
       </c>
       <c r="J111" t="n">
-        <v>-22.4068</v>
+        <v>-21.3356</v>
       </c>
     </row>
     <row r="112">
@@ -5909,10 +5909,10 @@
         <v>1.48</v>
       </c>
       <c r="I112" t="n">
-        <v>1.2504</v>
+        <v>0.8797</v>
       </c>
       <c r="J112" t="n">
-        <v>37.512</v>
+        <v>26.391</v>
       </c>
     </row>
     <row r="113">
@@ -5949,10 +5949,10 @@
         <v>1.23</v>
       </c>
       <c r="I113" t="n">
-        <v>0.7010999999999999</v>
+        <v>0.5315</v>
       </c>
       <c r="J113" t="n">
-        <v>21.033</v>
+        <v>15.945</v>
       </c>
     </row>
     <row r="114">
@@ -5989,10 +5989,10 @@
         <v>1.05</v>
       </c>
       <c r="I114" t="n">
-        <v>0.16</v>
+        <v>0.1835</v>
       </c>
       <c r="J114" t="n">
-        <v>4.8</v>
+        <v>5.505</v>
       </c>
     </row>
     <row r="115">
@@ -6029,10 +6029,10 @@
         <v>0.8</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.6924</v>
+        <v>-0.641</v>
       </c>
       <c r="J115" t="n">
-        <v>-20.772</v>
+        <v>-19.23</v>
       </c>
     </row>
     <row r="116">
@@ -6069,10 +6069,10 @@
         <v>0.78</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.7408</v>
+        <v>-0.6926</v>
       </c>
       <c r="J116" t="n">
-        <v>-22.224</v>
+        <v>-20.778</v>
       </c>
     </row>
     <row r="117">
@@ -6109,10 +6109,10 @@
         <v>1.08</v>
       </c>
       <c r="I117" t="n">
-        <v>0.2248</v>
+        <v>0.228</v>
       </c>
       <c r="J117" t="n">
-        <v>6.744</v>
+        <v>6.84</v>
       </c>
     </row>
     <row r="118">
@@ -6149,10 +6149,10 @@
         <v>1.05</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1693</v>
+        <v>0.1602</v>
       </c>
       <c r="J118" t="n">
-        <v>5.079</v>
+        <v>4.806</v>
       </c>
     </row>
     <row r="119">
@@ -6189,10 +6189,10 @@
         <v>0.93</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.125</v>
+        <v>-0.0929</v>
       </c>
       <c r="J119" t="n">
-        <v>-3.75</v>
+        <v>-2.787</v>
       </c>
     </row>
     <row r="120">
@@ -6229,10 +6229,10 @@
         <v>0.85</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2829</v>
+        <v>-0.1784</v>
       </c>
       <c r="J120" t="n">
-        <v>-8.487</v>
+        <v>-5.352</v>
       </c>
     </row>
     <row r="121">
@@ -6269,10 +6269,10 @@
         <v>0.68</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.5302</v>
+        <v>-0.3455</v>
       </c>
       <c r="J121" t="n">
-        <v>-15.906</v>
+        <v>-10.365</v>
       </c>
     </row>
     <row r="122">
@@ -6309,10 +6309,10 @@
         <v>1.46</v>
       </c>
       <c r="I122" t="n">
-        <v>1.1411</v>
+        <v>0.8162</v>
       </c>
       <c r="J122" t="n">
-        <v>28.5275</v>
+        <v>20.405</v>
       </c>
     </row>
     <row r="123">
@@ -6349,10 +6349,10 @@
         <v>1.44</v>
       </c>
       <c r="I123" t="n">
-        <v>1.0998</v>
+        <v>0.7903</v>
       </c>
       <c r="J123" t="n">
-        <v>27.495</v>
+        <v>19.7575</v>
       </c>
     </row>
     <row r="124">
@@ -6389,10 +6389,10 @@
         <v>1.11</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2651</v>
+        <v>0.3277</v>
       </c>
       <c r="J124" t="n">
-        <v>6.6275</v>
+        <v>8.192500000000001</v>
       </c>
     </row>
     <row r="125">
@@ -6429,10 +6429,10 @@
         <v>1.04</v>
       </c>
       <c r="I125" t="n">
-        <v>0.05</v>
+        <v>0.1192</v>
       </c>
       <c r="J125" t="n">
-        <v>1.25</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="126">
@@ -6469,10 +6469,10 @@
         <v>0.95</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3285</v>
+        <v>-0.2504</v>
       </c>
       <c r="J126" t="n">
-        <v>-8.2125</v>
+        <v>-6.26</v>
       </c>
     </row>
     <row r="127">
@@ -6509,10 +6509,10 @@
         <v>0.98</v>
       </c>
       <c r="I127" t="n">
-        <v>0.0484</v>
+        <v>-0.0002</v>
       </c>
       <c r="J127" t="n">
-        <v>1.21</v>
+        <v>-0.005</v>
       </c>
     </row>
     <row r="128">
@@ -6549,10 +6549,10 @@
         <v>0.77</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.3367</v>
+        <v>-0.2409</v>
       </c>
       <c r="J128" t="n">
-        <v>-8.4175</v>
+        <v>-6.0225</v>
       </c>
     </row>
     <row r="129">
@@ -6589,10 +6589,10 @@
         <v>0.74</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.3945</v>
+        <v>-0.2686</v>
       </c>
       <c r="J129" t="n">
-        <v>-9.862500000000001</v>
+        <v>-6.715</v>
       </c>
     </row>
     <row r="130">
@@ -6629,10 +6629,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.4729</v>
+        <v>-0.3157</v>
       </c>
       <c r="J130" t="n">
-        <v>-11.8225</v>
+        <v>-7.8925</v>
       </c>
     </row>
     <row r="131">
@@ -6669,10 +6669,10 @@
         <v>0.67</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5023</v>
+        <v>-0.3345</v>
       </c>
       <c r="J131" t="n">
-        <v>-12.5575</v>
+        <v>-8.362500000000001</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/1886/event_1886_evp_summary.xlsx
+++ b/database/event/1886/event_1886_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.6507</v>
+        <v>4.5679</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1.4615</v>
+        <v>1.4552</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6507</v>
+        <v>4.5679</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5793</v>
+        <v>2.4652</v>
       </c>
       <c r="G2" t="n">
-        <v>2.0714</v>
+        <v>2.1027</v>
       </c>
       <c r="H2" t="n">
-        <v>3.6015</v>
+        <v>3.2395</v>
       </c>
       <c r="I2" t="n">
-        <v>1.8726</v>
+        <v>1.7493</v>
       </c>
       <c r="J2" t="n">
-        <v>2.0714</v>
+        <v>2.1027</v>
       </c>
       <c r="K2" t="n">
         <v>58</v>
@@ -529,7 +529,7 @@
         <v>85</v>
       </c>
       <c r="M2" t="n">
-        <v>3.944</v>
+        <v>3.852</v>
       </c>
       <c r="N2" t="n">
         <v>143</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.4841</v>
+        <v>3.3731</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9349</v>
+        <v>0.9113</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4841</v>
+        <v>3.3731</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1826</v>
+        <v>0.9567</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3015</v>
+        <v>2.4164</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1826</v>
+        <v>0.9567</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6149</v>
+        <v>0.5165999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>2.3015</v>
+        <v>2.4164</v>
       </c>
       <c r="K3" t="n">
         <v>114</v>
@@ -575,7 +575,7 @@
         <v>84</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9164</v>
+        <v>2.933</v>
       </c>
       <c r="N3" t="n">
         <v>198</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.2917</v>
+        <v>3.2292</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.848</v>
+        <v>0.8458</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2917</v>
+        <v>3.2292</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8453</v>
+        <v>2.7506</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4464</v>
+        <v>0.4786</v>
       </c>
       <c r="H4" t="n">
-        <v>4.5389</v>
+        <v>4.1812</v>
       </c>
       <c r="I4" t="n">
-        <v>2.36</v>
+        <v>2.2578</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4464</v>
+        <v>0.4786</v>
       </c>
       <c r="K4" t="n">
         <v>132</v>
@@ -621,7 +621,7 @@
         <v>56</v>
       </c>
       <c r="M4" t="n">
-        <v>2.8064</v>
+        <v>2.7364</v>
       </c>
       <c r="N4" t="n">
         <v>188</v>
@@ -630,93 +630,93 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.7328</v>
+        <v>2.7951</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5957</v>
+        <v>0.6482</v>
       </c>
       <c r="E5" t="n">
-        <v>2.7328</v>
+        <v>2.7951</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5215</v>
+        <v>0.4635</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2113</v>
+        <v>2.3316</v>
       </c>
       <c r="H5" t="n">
-        <v>3.398</v>
+        <v>0.4635</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7668</v>
+        <v>0.2503</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2113</v>
+        <v>2.3316</v>
       </c>
       <c r="K5" t="n">
-        <v>58</v>
+        <v>114</v>
       </c>
       <c r="L5" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M5" t="n">
-        <v>1.9781</v>
+        <v>2.5819</v>
       </c>
       <c r="N5" t="n">
-        <v>143</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.64</v>
+        <v>2.7655</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5538</v>
+        <v>0.6347</v>
       </c>
       <c r="E6" t="n">
-        <v>2.64</v>
+        <v>2.7655</v>
       </c>
       <c r="F6" t="n">
-        <v>0.422</v>
+        <v>2.4376</v>
       </c>
       <c r="G6" t="n">
-        <v>2.218</v>
+        <v>0.3279</v>
       </c>
       <c r="H6" t="n">
-        <v>0.422</v>
+        <v>3.1482</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2194</v>
+        <v>1.7</v>
       </c>
       <c r="J6" t="n">
-        <v>2.218</v>
+        <v>0.3279</v>
       </c>
       <c r="K6" t="n">
-        <v>114</v>
+        <v>58</v>
       </c>
       <c r="L6" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M6" t="n">
-        <v>2.4374</v>
+        <v>2.0279</v>
       </c>
       <c r="N6" t="n">
-        <v>198</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7">
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.3946</v>
+        <v>2.257</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.443</v>
+        <v>0.4032</v>
       </c>
       <c r="E7" t="n">
-        <v>2.3946</v>
+        <v>2.257</v>
       </c>
       <c r="F7" t="n">
-        <v>2.6828</v>
+        <v>2.5774</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2882</v>
+        <v>-0.3204</v>
       </c>
       <c r="H7" t="n">
-        <v>3.9663</v>
+        <v>3.6097</v>
       </c>
       <c r="I7" t="n">
-        <v>2.0623</v>
+        <v>1.9492</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2882</v>
+        <v>-0.3204</v>
       </c>
       <c r="K7" t="n">
         <v>132</v>
@@ -759,7 +759,7 @@
         <v>56</v>
       </c>
       <c r="M7" t="n">
-        <v>1.7741</v>
+        <v>1.6288</v>
       </c>
       <c r="N7" t="n">
         <v>188</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8686</v>
+        <v>0.7658</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2459</v>
+        <v>-0.2756</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8686</v>
+        <v>0.7658</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9493</v>
+        <v>0.863</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.08069999999999999</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9493</v>
+        <v>0.863</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4936</v>
+        <v>0.466</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.08069999999999999</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="K8" t="n">
         <v>76</v>
@@ -805,7 +805,7 @@
         <v>55</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4129</v>
+        <v>0.3688</v>
       </c>
       <c r="N8" t="n">
         <v>131</v>
@@ -814,93 +814,93 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5566</v>
+        <v>0.5598</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3867</v>
+        <v>-0.3694</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5566</v>
+        <v>0.5598</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3687</v>
+        <v>-1.4193</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1879</v>
+        <v>1.9791</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3687</v>
+        <v>-1.4193</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1917</v>
+        <v>-0.7664</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1879</v>
+        <v>1.9791</v>
       </c>
       <c r="K9" t="n">
-        <v>114</v>
+        <v>58</v>
       </c>
       <c r="L9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3796</v>
+        <v>1.2127</v>
       </c>
       <c r="N9" t="n">
-        <v>198</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4544</v>
+        <v>0.4822</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4329</v>
+        <v>-0.4047</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4544</v>
+        <v>0.4822</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5649</v>
+        <v>0.2783</v>
       </c>
       <c r="G10" t="n">
-        <v>2.0193</v>
+        <v>0.2039</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.5649</v>
+        <v>0.2783</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8137</v>
+        <v>0.1503</v>
       </c>
       <c r="J10" t="n">
-        <v>2.0193</v>
+        <v>0.2039</v>
       </c>
       <c r="K10" t="n">
-        <v>58</v>
+        <v>114</v>
       </c>
       <c r="L10" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M10" t="n">
-        <v>1.2056</v>
+        <v>0.3542</v>
       </c>
       <c r="N10" t="n">
-        <v>143</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11">
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4517</v>
+        <v>0.2835</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4341</v>
+        <v>-0.4951</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4517</v>
+        <v>0.2835</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9941</v>
+        <v>0.8528</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5424</v>
+        <v>-0.5693</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9941</v>
+        <v>0.8528</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5169</v>
+        <v>0.4605</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5424</v>
+        <v>-0.5693</v>
       </c>
       <c r="K11" t="n">
         <v>132</v>
@@ -943,7 +943,7 @@
         <v>56</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.02549999999999997</v>
+        <v>-0.1088</v>
       </c>
       <c r="N11" t="n">
         <v>188</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2419</v>
+        <v>0.0704</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.5288</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2419</v>
+        <v>0.0704</v>
       </c>
       <c r="F12" t="n">
-        <v>1.679</v>
+        <v>1.4767</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.4371</v>
+        <v>-1.4063</v>
       </c>
       <c r="H12" t="n">
-        <v>1.679</v>
+        <v>1.4767</v>
       </c>
       <c r="I12" t="n">
-        <v>0.873</v>
+        <v>0.7974</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.4371</v>
+        <v>-1.4063</v>
       </c>
       <c r="K12" t="n">
         <v>114</v>
@@ -989,7 +989,7 @@
         <v>84</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.5641</v>
+        <v>-0.6089000000000001</v>
       </c>
       <c r="N12" t="n">
         <v>198</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.1958</v>
+        <v>-0.2648</v>
       </c>
       <c r="C13" t="n">
         <v>-0</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.7264</v>
+        <v>-0.7447</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1958</v>
+        <v>-0.2648</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1081</v>
+        <v>-0.1606</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0877</v>
+        <v>-0.1042</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1081</v>
+        <v>-0.1606</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0562</v>
+        <v>-0.0867</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.0877</v>
+        <v>-0.1042</v>
       </c>
       <c r="K13" t="n">
         <v>76</v>
@@ -1035,7 +1035,7 @@
         <v>55</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.1439</v>
+        <v>-0.1909</v>
       </c>
       <c r="N13" t="n">
         <v>131</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.6761</v>
+        <v>-0.4398</v>
       </c>
       <c r="C14" t="n">
         <v>-0</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.9432</v>
+        <v>-0.8244</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.6761</v>
+        <v>-0.4398</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0412</v>
+        <v>0.062</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.7173</v>
+        <v>-0.5018</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0412</v>
+        <v>0.062</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0214</v>
+        <v>0.0335</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.7173</v>
+        <v>-0.5018</v>
       </c>
       <c r="K14" t="n">
         <v>58</v>
@@ -1081,7 +1081,7 @@
         <v>85</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.6959000000000001</v>
+        <v>-0.4683</v>
       </c>
       <c r="N14" t="n">
         <v>143</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-1.0309</v>
+        <v>-1.0501</v>
       </c>
       <c r="C15" t="n">
         <v>-0</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.1034</v>
+        <v>-1.1022</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.0309</v>
+        <v>-1.0501</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9378</v>
+        <v>-0.9291</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0931</v>
+        <v>-0.121</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.9378</v>
+        <v>-0.9291</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4876</v>
+        <v>-0.5017</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.0931</v>
+        <v>-0.121</v>
       </c>
       <c r="K15" t="n">
         <v>76</v>
@@ -1127,7 +1127,7 @@
         <v>55</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5807</v>
+        <v>-0.6227</v>
       </c>
       <c r="N15" t="n">
         <v>131</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-1.0596</v>
+        <v>-1.0672</v>
       </c>
       <c r="C16" t="n">
         <v>-0</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.1164</v>
+        <v>-1.11</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.0596</v>
+        <v>-1.0672</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9076</v>
+        <v>-0.8924</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.152</v>
+        <v>-0.1748</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.9076</v>
+        <v>-0.8924</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4719</v>
+        <v>-0.4819</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.152</v>
+        <v>-0.1748</v>
       </c>
       <c r="K16" t="n">
         <v>132</v>
@@ -1173,7 +1173,7 @@
         <v>56</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6239</v>
+        <v>-0.6567000000000001</v>
       </c>
       <c r="N16" t="n">
         <v>188</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-1.2548</v>
+        <v>-1.196</v>
       </c>
       <c r="C17" t="n">
         <v>-0</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.2045</v>
+        <v>-1.1686</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.2548</v>
+        <v>-1.196</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4466</v>
+        <v>-0.3902</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8082</v>
+        <v>-0.8058</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4466</v>
+        <v>-0.3902</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2322</v>
+        <v>-0.2107</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.8082</v>
+        <v>-0.8058</v>
       </c>
       <c r="K17" t="n">
         <v>58</v>
@@ -1219,7 +1219,7 @@
         <v>85</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0404</v>
+        <v>-1.0165</v>
       </c>
       <c r="N17" t="n">
         <v>143</v>
@@ -1228,35 +1228,35 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>adreN</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-1.2697</v>
+        <v>-1.3348</v>
       </c>
       <c r="C18" t="n">
         <v>-0</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2112</v>
+        <v>-1.2318</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2697</v>
+        <v>-1.3348</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6556</v>
+        <v>-0.7891</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6141</v>
+        <v>-0.5457</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6556</v>
+        <v>-0.7891</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3409</v>
+        <v>-0.4261</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6141</v>
+        <v>-0.5457</v>
       </c>
       <c r="K18" t="n">
         <v>76</v>
@@ -1265,7 +1265,7 @@
         <v>55</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.955</v>
+        <v>-0.9718</v>
       </c>
       <c r="N18" t="n">
         <v>131</v>
@@ -1274,35 +1274,35 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>adreN</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-1.2701</v>
+        <v>-1.3426</v>
       </c>
       <c r="C19" t="n">
         <v>-0</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2114</v>
+        <v>-1.2354</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2701</v>
+        <v>-1.3426</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7572</v>
+        <v>-0.6967</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5129</v>
+        <v>-0.6459</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7572</v>
+        <v>-0.6967</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3937</v>
+        <v>-0.3762</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5129</v>
+        <v>-0.6459</v>
       </c>
       <c r="K19" t="n">
         <v>76</v>
@@ -1311,7 +1311,7 @@
         <v>55</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9066000000000001</v>
+        <v>-1.0221</v>
       </c>
       <c r="N19" t="n">
         <v>131</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-1.3402</v>
+        <v>-1.3929</v>
       </c>
       <c r="C20" t="n">
         <v>-0</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.243</v>
+        <v>-1.2583</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3402</v>
+        <v>-1.3929</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2769</v>
+        <v>-0.3619</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0633</v>
+        <v>-1.031</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2769</v>
+        <v>-0.3619</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.144</v>
+        <v>-0.1954</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.0633</v>
+        <v>-1.031</v>
       </c>
       <c r="K20" t="n">
         <v>114</v>
@@ -1357,7 +1357,7 @@
         <v>84</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2073</v>
+        <v>-1.2264</v>
       </c>
       <c r="N20" t="n">
         <v>198</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-3.3467</v>
+        <v>-3.255</v>
       </c>
       <c r="C21" t="n">
         <v>-0</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1489</v>
+        <v>-2.1059</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.3467</v>
+        <v>-3.255</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.6802</v>
+        <v>-2.5602</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6665</v>
+        <v>-0.6948</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.6802</v>
+        <v>-2.5602</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.3936</v>
+        <v>-1.3825</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6665</v>
+        <v>-0.6948</v>
       </c>
       <c r="K21" t="n">
         <v>132</v>
@@ -1403,7 +1403,7 @@
         <v>56</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.0601</v>
+        <v>-2.0773</v>
       </c>
       <c r="N21" t="n">
         <v>188</v>
@@ -1509,10 +1509,10 @@
         <v>1.34</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8995</v>
+        <v>0.8433</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8995</v>
+        <v>0.8433</v>
       </c>
     </row>
     <row r="3">
@@ -1549,10 +1549,10 @@
         <v>1.27</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7363</v>
+        <v>0.7002</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7363</v>
+        <v>0.7002</v>
       </c>
     </row>
     <row r="4">
@@ -1589,10 +1589,10 @@
         <v>1.26</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7125</v>
+        <v>0.6792</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7125</v>
+        <v>0.6792</v>
       </c>
     </row>
     <row r="5">
@@ -1629,10 +1629,10 @@
         <v>1.17</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4942</v>
+        <v>0.4839</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4942</v>
+        <v>0.4839</v>
       </c>
     </row>
     <row r="6">
@@ -1669,10 +1669,10 @@
         <v>0.74</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8163</v>
+        <v>-0.752</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.8163</v>
+        <v>-0.752</v>
       </c>
     </row>
     <row r="7">
@@ -1709,10 +1709,10 @@
         <v>1.18</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4393</v>
+        <v>0.4269</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4393</v>
+        <v>0.4269</v>
       </c>
     </row>
     <row r="8">
@@ -1749,10 +1749,10 @@
         <v>0.88</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.145</v>
+        <v>-0.1608</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.145</v>
+        <v>-0.1608</v>
       </c>
     </row>
     <row r="9">
@@ -1789,10 +1789,10 @@
         <v>0.87</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1555</v>
+        <v>-0.1714</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1555</v>
+        <v>-0.1714</v>
       </c>
     </row>
     <row r="10">
@@ -1829,10 +1829,10 @@
         <v>0.87</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1555</v>
+        <v>-0.1714</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1555</v>
+        <v>-0.1714</v>
       </c>
     </row>
     <row r="11">
@@ -1869,10 +1869,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3334</v>
+        <v>-0.3472</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3334</v>
+        <v>-0.3472</v>
       </c>
     </row>
     <row r="12">
@@ -1909,10 +1909,10 @@
         <v>1.4</v>
       </c>
       <c r="I12" t="n">
-        <v>1.0571</v>
+        <v>1.0047</v>
       </c>
       <c r="J12" t="n">
-        <v>29.5988</v>
+        <v>28.1316</v>
       </c>
     </row>
     <row r="13">
@@ -1949,10 +1949,10 @@
         <v>1.12</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3952</v>
+        <v>0.3867</v>
       </c>
       <c r="J13" t="n">
-        <v>11.0656</v>
+        <v>10.8276</v>
       </c>
     </row>
     <row r="14">
@@ -1989,10 +1989,10 @@
         <v>0.92</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2986</v>
+        <v>-0.2935</v>
       </c>
       <c r="J14" t="n">
-        <v>-8.360799999999999</v>
+        <v>-8.218</v>
       </c>
     </row>
     <row r="15">
@@ -2029,10 +2029,10 @@
         <v>0.86</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.47</v>
+        <v>-0.4505</v>
       </c>
       <c r="J15" t="n">
-        <v>-13.16</v>
+        <v>-12.614</v>
       </c>
     </row>
     <row r="16">
@@ -2069,10 +2069,10 @@
         <v>0.85</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4973</v>
+        <v>-0.4751</v>
       </c>
       <c r="J16" t="n">
-        <v>-13.9244</v>
+        <v>-13.3028</v>
       </c>
     </row>
     <row r="17">
@@ -2109,10 +2109,10 @@
         <v>1.37</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7611</v>
+        <v>0.7235</v>
       </c>
       <c r="J17" t="n">
-        <v>21.3108</v>
+        <v>20.258</v>
       </c>
     </row>
     <row r="18">
@@ -2149,10 +2149,10 @@
         <v>1.2</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4569</v>
+        <v>0.4471</v>
       </c>
       <c r="J18" t="n">
-        <v>12.7932</v>
+        <v>12.5188</v>
       </c>
     </row>
     <row r="19">
@@ -2189,10 +2189,10 @@
         <v>1.08</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2186</v>
+        <v>0.2223</v>
       </c>
       <c r="J19" t="n">
-        <v>6.1208</v>
+        <v>6.2244</v>
       </c>
     </row>
     <row r="20">
@@ -2229,10 +2229,10 @@
         <v>0.68</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3491</v>
+        <v>-0.3612</v>
       </c>
       <c r="J20" t="n">
-        <v>-9.774800000000001</v>
+        <v>-10.1136</v>
       </c>
     </row>
     <row r="21">
@@ -2269,10 +2269,10 @@
         <v>0.41</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5945</v>
+        <v>-0.5943000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>-16.646</v>
+        <v>-16.6404</v>
       </c>
     </row>
     <row r="22">
@@ -2309,10 +2309,10 @@
         <v>1.07</v>
       </c>
       <c r="I22" t="n">
-        <v>0.239</v>
+        <v>0.2321</v>
       </c>
       <c r="J22" t="n">
-        <v>6.692</v>
+        <v>6.4988</v>
       </c>
     </row>
     <row r="23">
@@ -2349,10 +2349,10 @@
         <v>1.02</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1137</v>
+        <v>0.108</v>
       </c>
       <c r="J23" t="n">
-        <v>3.1836</v>
+        <v>3.024</v>
       </c>
     </row>
     <row r="24">
@@ -2389,10 +2389,10 @@
         <v>0.89</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1278</v>
+        <v>-0.1448</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.5784</v>
+        <v>-4.0544</v>
       </c>
     </row>
     <row r="25">
@@ -2429,10 +2429,10 @@
         <v>0.8</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2186</v>
+        <v>-0.2366</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.1208</v>
+        <v>-6.6248</v>
       </c>
     </row>
     <row r="26">
@@ -2469,10 +2469,10 @@
         <v>0.38</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6104000000000001</v>
+        <v>-0.6107</v>
       </c>
       <c r="J26" t="n">
-        <v>-17.0912</v>
+        <v>-17.0996</v>
       </c>
     </row>
     <row r="27">
@@ -2509,10 +2509,10 @@
         <v>1.35</v>
       </c>
       <c r="I27" t="n">
-        <v>0.913</v>
+        <v>0.8569</v>
       </c>
       <c r="J27" t="n">
-        <v>25.564</v>
+        <v>23.9932</v>
       </c>
     </row>
     <row r="28">
@@ -2549,10 +2549,10 @@
         <v>1.32</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8449</v>
+        <v>0.797</v>
       </c>
       <c r="J28" t="n">
-        <v>23.6572</v>
+        <v>22.316</v>
       </c>
     </row>
     <row r="29">
@@ -2589,10 +2589,10 @@
         <v>1.22</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6105</v>
+        <v>0.5899</v>
       </c>
       <c r="J29" t="n">
-        <v>17.094</v>
+        <v>16.5172</v>
       </c>
     </row>
     <row r="30">
@@ -2629,10 +2629,10 @@
         <v>1.2</v>
       </c>
       <c r="I30" t="n">
-        <v>0.5627</v>
+        <v>0.5469000000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>15.7556</v>
+        <v>15.3132</v>
       </c>
     </row>
     <row r="31">
@@ -2669,10 +2669,10 @@
         <v>0.82</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6187</v>
+        <v>-0.5759</v>
       </c>
       <c r="J31" t="n">
-        <v>-17.3236</v>
+        <v>-16.1252</v>
       </c>
     </row>
     <row r="32">
@@ -2709,10 +2709,10 @@
         <v>1.44</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8499</v>
+        <v>0.8074</v>
       </c>
       <c r="J32" t="n">
-        <v>23.7972</v>
+        <v>22.6072</v>
       </c>
     </row>
     <row r="33">
@@ -2749,10 +2749,10 @@
         <v>1.26</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5434</v>
+        <v>0.5308</v>
       </c>
       <c r="J33" t="n">
-        <v>15.2152</v>
+        <v>14.8624</v>
       </c>
     </row>
     <row r="34">
@@ -2789,10 +2789,10 @@
         <v>1.05</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1374</v>
+        <v>0.1465</v>
       </c>
       <c r="J34" t="n">
-        <v>3.8472</v>
+        <v>4.102</v>
       </c>
     </row>
     <row r="35">
@@ -2829,10 +2829,10 @@
         <v>0.92</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1127</v>
+        <v>-0.1245</v>
       </c>
       <c r="J35" t="n">
-        <v>-3.1556</v>
+        <v>-3.486</v>
       </c>
     </row>
     <row r="36">
@@ -2869,10 +2869,10 @@
         <v>0.38</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6256</v>
+        <v>-0.6227</v>
       </c>
       <c r="J36" t="n">
-        <v>-17.5168</v>
+        <v>-17.4356</v>
       </c>
     </row>
     <row r="37">
@@ -2909,10 +2909,10 @@
         <v>1.33</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9458</v>
+        <v>0.8735000000000001</v>
       </c>
       <c r="J37" t="n">
-        <v>26.4824</v>
+        <v>24.458</v>
       </c>
     </row>
     <row r="38">
@@ -2949,10 +2949,10 @@
         <v>1.18</v>
       </c>
       <c r="I38" t="n">
-        <v>0.5696</v>
+        <v>0.5414</v>
       </c>
       <c r="J38" t="n">
-        <v>15.9488</v>
+        <v>15.1592</v>
       </c>
     </row>
     <row r="39">
@@ -2989,10 +2989,10 @@
         <v>0.92</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.2896</v>
+        <v>-0.2873</v>
       </c>
       <c r="J39" t="n">
-        <v>-8.1088</v>
+        <v>-8.0444</v>
       </c>
     </row>
     <row r="40">
@@ -3029,10 +3029,10 @@
         <v>0.8</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.6205000000000001</v>
+        <v>-0.587</v>
       </c>
       <c r="J40" t="n">
-        <v>-17.374</v>
+        <v>-16.436</v>
       </c>
     </row>
     <row r="41">
@@ -3069,10 +3069,10 @@
         <v>0.76</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.7233000000000001</v>
+        <v>-0.6777</v>
       </c>
       <c r="J41" t="n">
-        <v>-20.2524</v>
+        <v>-18.9756</v>
       </c>
     </row>
     <row r="42">
@@ -3109,10 +3109,10 @@
         <v>1.34</v>
       </c>
       <c r="I42" t="n">
-        <v>0.6963</v>
+        <v>0.6673</v>
       </c>
       <c r="J42" t="n">
-        <v>19.4964</v>
+        <v>18.6844</v>
       </c>
     </row>
     <row r="43">
@@ -3149,10 +3149,10 @@
         <v>1.05</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1445</v>
+        <v>0.1516</v>
       </c>
       <c r="J43" t="n">
-        <v>4.046</v>
+        <v>4.2448</v>
       </c>
     </row>
     <row r="44">
@@ -3189,10 +3189,10 @@
         <v>0.98</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.0344</v>
+        <v>-0.0416</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.9631999999999999</v>
+        <v>-1.1648</v>
       </c>
     </row>
     <row r="45">
@@ -3229,10 +3229,10 @@
         <v>0.91</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1204</v>
+        <v>-0.1334</v>
       </c>
       <c r="J45" t="n">
-        <v>-3.3712</v>
+        <v>-3.7352</v>
       </c>
     </row>
     <row r="46">
@@ -3269,10 +3269,10 @@
         <v>0.6</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4267</v>
+        <v>-0.4352</v>
       </c>
       <c r="J46" t="n">
-        <v>-11.9476</v>
+        <v>-12.1856</v>
       </c>
     </row>
     <row r="47">
@@ -3309,10 +3309,10 @@
         <v>1.48</v>
       </c>
       <c r="I47" t="n">
-        <v>1.1443</v>
+        <v>1.1019</v>
       </c>
       <c r="J47" t="n">
-        <v>32.0404</v>
+        <v>30.8532</v>
       </c>
     </row>
     <row r="48">
@@ -3349,10 +3349,10 @@
         <v>1.36</v>
       </c>
       <c r="I48" t="n">
-        <v>0.9651</v>
+        <v>0.9003</v>
       </c>
       <c r="J48" t="n">
-        <v>27.0228</v>
+        <v>25.2084</v>
       </c>
     </row>
     <row r="49">
@@ -3389,10 +3389,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2553</v>
+        <v>-0.2486</v>
       </c>
       <c r="J49" t="n">
-        <v>-7.1484</v>
+        <v>-6.9608</v>
       </c>
     </row>
     <row r="50">
@@ -3429,10 +3429,10 @@
         <v>0.9</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3761</v>
+        <v>-0.361</v>
       </c>
       <c r="J50" t="n">
-        <v>-10.5308</v>
+        <v>-10.108</v>
       </c>
     </row>
     <row r="51">
@@ -3469,10 +3469,10 @@
         <v>0.8</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6487000000000001</v>
+        <v>-0.6068</v>
       </c>
       <c r="J51" t="n">
-        <v>-18.1636</v>
+        <v>-16.9904</v>
       </c>
     </row>
     <row r="52">
@@ -3509,10 +3509,10 @@
         <v>1.07</v>
       </c>
       <c r="I52" t="n">
-        <v>0.2355</v>
+        <v>0.2295</v>
       </c>
       <c r="J52" t="n">
-        <v>7.065</v>
+        <v>6.885</v>
       </c>
     </row>
     <row r="53">
@@ -3549,10 +3549,10 @@
         <v>0.92</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.0948</v>
+        <v>-0.1107</v>
       </c>
       <c r="J53" t="n">
-        <v>-2.844</v>
+        <v>-3.321</v>
       </c>
     </row>
     <row r="54">
@@ -3589,10 +3589,10 @@
         <v>0.87</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1504</v>
+        <v>-0.1675</v>
       </c>
       <c r="J54" t="n">
-        <v>-4.512</v>
+        <v>-5.025</v>
       </c>
     </row>
     <row r="55">
@@ -3629,10 +3629,10 @@
         <v>0.7</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3161</v>
+        <v>-0.3319</v>
       </c>
       <c r="J55" t="n">
-        <v>-9.483000000000001</v>
+        <v>-9.957000000000001</v>
       </c>
     </row>
     <row r="56">
@@ -3669,10 +3669,10 @@
         <v>0.64</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3729</v>
+        <v>-0.3866</v>
       </c>
       <c r="J56" t="n">
-        <v>-11.187</v>
+        <v>-11.598</v>
       </c>
     </row>
     <row r="57">
@@ -3709,10 +3709,10 @@
         <v>1.34</v>
       </c>
       <c r="I57" t="n">
-        <v>0.9075</v>
+        <v>0.849</v>
       </c>
       <c r="J57" t="n">
-        <v>27.225</v>
+        <v>25.47</v>
       </c>
     </row>
     <row r="58">
@@ -3749,10 +3749,10 @@
         <v>1.22</v>
       </c>
       <c r="I58" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.5981</v>
       </c>
       <c r="J58" t="n">
-        <v>18.675</v>
+        <v>17.943</v>
       </c>
     </row>
     <row r="59">
@@ -3789,10 +3789,10 @@
         <v>1.13</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3975</v>
+        <v>0.3945</v>
       </c>
       <c r="J59" t="n">
-        <v>11.925</v>
+        <v>11.835</v>
       </c>
     </row>
     <row r="60">
@@ -3829,10 +3829,10 @@
         <v>1.01</v>
       </c>
       <c r="I60" t="n">
-        <v>0.0231</v>
+        <v>0.0379</v>
       </c>
       <c r="J60" t="n">
-        <v>0.6929999999999999</v>
+        <v>1.137</v>
       </c>
     </row>
     <row r="61">
@@ -3869,10 +3869,10 @@
         <v>0.97</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.165</v>
+        <v>-0.1596</v>
       </c>
       <c r="J61" t="n">
-        <v>-4.95</v>
+        <v>-4.788</v>
       </c>
     </row>
     <row r="62">
@@ -3909,10 +3909,10 @@
         <v>1.17</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4649</v>
+        <v>0.4421</v>
       </c>
       <c r="J62" t="n">
-        <v>11.6225</v>
+        <v>11.0525</v>
       </c>
     </row>
     <row r="63">
@@ -3949,10 +3949,10 @@
         <v>1.08</v>
       </c>
       <c r="I63" t="n">
-        <v>0.2733</v>
+        <v>0.2624</v>
       </c>
       <c r="J63" t="n">
-        <v>6.8325</v>
+        <v>6.56</v>
       </c>
     </row>
     <row r="64">
@@ -3989,10 +3989,10 @@
         <v>0.83</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1875</v>
+        <v>-0.2059</v>
       </c>
       <c r="J64" t="n">
-        <v>-4.6875</v>
+        <v>-5.1475</v>
       </c>
     </row>
     <row r="65">
@@ -4029,10 +4029,10 @@
         <v>0.51</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.4893</v>
+        <v>-0.4977</v>
       </c>
       <c r="J65" t="n">
-        <v>-12.2325</v>
+        <v>-12.4425</v>
       </c>
     </row>
     <row r="66">
@@ -4069,10 +4069,10 @@
         <v>0.45</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5443</v>
+        <v>-0.5494</v>
       </c>
       <c r="J66" t="n">
-        <v>-13.6075</v>
+        <v>-13.735</v>
       </c>
     </row>
     <row r="67">
@@ -4109,10 +4109,10 @@
         <v>1.45</v>
       </c>
       <c r="I67" t="n">
-        <v>1.0861</v>
+        <v>1.0414</v>
       </c>
       <c r="J67" t="n">
-        <v>27.1525</v>
+        <v>26.035</v>
       </c>
     </row>
     <row r="68">
@@ -4149,10 +4149,10 @@
         <v>1.38</v>
       </c>
       <c r="I68" t="n">
-        <v>0.9809</v>
+        <v>0.9207</v>
       </c>
       <c r="J68" t="n">
-        <v>24.5225</v>
+        <v>23.0175</v>
       </c>
     </row>
     <row r="69">
@@ -4189,10 +4189,10 @@
         <v>1.14</v>
       </c>
       <c r="I69" t="n">
-        <v>0.4188</v>
+        <v>0.4151</v>
       </c>
       <c r="J69" t="n">
-        <v>10.47</v>
+        <v>10.3775</v>
       </c>
     </row>
     <row r="70">
@@ -4229,10 +4229,10 @@
         <v>1.03</v>
       </c>
       <c r="I70" t="n">
-        <v>0.094</v>
+        <v>0.1108</v>
       </c>
       <c r="J70" t="n">
-        <v>2.35</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="71">
@@ -4269,10 +4269,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6399</v>
+        <v>-0.5957</v>
       </c>
       <c r="J71" t="n">
-        <v>-15.9975</v>
+        <v>-14.8925</v>
       </c>
     </row>
     <row r="72">
@@ -4309,10 +4309,10 @@
         <v>1.48</v>
       </c>
       <c r="I72" t="n">
-        <v>0.6208</v>
+        <v>0.6194</v>
       </c>
       <c r="J72" t="n">
-        <v>17.3824</v>
+        <v>17.3432</v>
       </c>
     </row>
     <row r="73">
@@ -4349,10 +4349,10 @@
         <v>1.21</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3033</v>
+        <v>0.3181</v>
       </c>
       <c r="J73" t="n">
-        <v>8.4924</v>
+        <v>8.9068</v>
       </c>
     </row>
     <row r="74">
@@ -4389,10 +4389,10 @@
         <v>1.1</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1613</v>
+        <v>0.1771</v>
       </c>
       <c r="J74" t="n">
-        <v>4.5164</v>
+        <v>4.9588</v>
       </c>
     </row>
     <row r="75">
@@ -4429,10 +4429,10 @@
         <v>0.93</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.1124</v>
+        <v>-0.1211</v>
       </c>
       <c r="J75" t="n">
-        <v>-3.1472</v>
+        <v>-3.3908</v>
       </c>
     </row>
     <row r="76">
@@ -4469,10 +4469,10 @@
         <v>0.86</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.1902</v>
+        <v>-0.2009</v>
       </c>
       <c r="J76" t="n">
-        <v>-5.3256</v>
+        <v>-5.6252</v>
       </c>
     </row>
     <row r="77">
@@ -4509,10 +4509,10 @@
         <v>1.17</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3497</v>
+        <v>0.3417</v>
       </c>
       <c r="J77" t="n">
-        <v>9.791600000000001</v>
+        <v>9.567600000000001</v>
       </c>
     </row>
     <row r="78">
@@ -4549,10 +4549,10 @@
         <v>0.89</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.1263</v>
+        <v>-0.1437</v>
       </c>
       <c r="J78" t="n">
-        <v>-3.5364</v>
+        <v>-4.0236</v>
       </c>
     </row>
     <row r="79">
@@ -4589,10 +4589,10 @@
         <v>0.83</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1889</v>
+        <v>-0.207</v>
       </c>
       <c r="J79" t="n">
-        <v>-5.2892</v>
+        <v>-5.796</v>
       </c>
     </row>
     <row r="80">
@@ -4629,10 +4629,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3231</v>
+        <v>-0.3392</v>
       </c>
       <c r="J80" t="n">
-        <v>-9.046799999999999</v>
+        <v>-9.4976</v>
       </c>
     </row>
     <row r="81">
@@ -4669,10 +4669,10 @@
         <v>0.53</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4727</v>
+        <v>-0.4818</v>
       </c>
       <c r="J81" t="n">
-        <v>-13.2356</v>
+        <v>-13.4904</v>
       </c>
     </row>
     <row r="82">
@@ -4709,10 +4709,10 @@
         <v>1.06</v>
       </c>
       <c r="I82" t="n">
-        <v>0.263</v>
+        <v>0.2444</v>
       </c>
       <c r="J82" t="n">
-        <v>6.049</v>
+        <v>5.6212</v>
       </c>
     </row>
     <row r="83">
@@ -4749,10 +4749,10 @@
         <v>0.82</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.1877</v>
+        <v>-0.2084</v>
       </c>
       <c r="J83" t="n">
-        <v>-4.3171</v>
+        <v>-4.7932</v>
       </c>
     </row>
     <row r="84">
@@ -4789,10 +4789,10 @@
         <v>0.73</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.2746</v>
+        <v>-0.2942</v>
       </c>
       <c r="J84" t="n">
-        <v>-6.3158</v>
+        <v>-6.7666</v>
       </c>
     </row>
     <row r="85">
@@ -4829,10 +4829,10 @@
         <v>0.57</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.424</v>
+        <v>-0.4377</v>
       </c>
       <c r="J85" t="n">
-        <v>-9.752000000000001</v>
+        <v>-10.0671</v>
       </c>
     </row>
     <row r="86">
@@ -4869,10 +4869,10 @@
         <v>0.53</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4614</v>
+        <v>-0.4729</v>
       </c>
       <c r="J86" t="n">
-        <v>-10.6122</v>
+        <v>-10.8767</v>
       </c>
     </row>
     <row r="87">
@@ -4909,10 +4909,10 @@
         <v>1.26</v>
       </c>
       <c r="I87" t="n">
-        <v>0.7219</v>
+        <v>0.6857</v>
       </c>
       <c r="J87" t="n">
-        <v>16.6037</v>
+        <v>15.7711</v>
       </c>
     </row>
     <row r="88">
@@ -4949,10 +4949,10 @@
         <v>1.24</v>
       </c>
       <c r="I88" t="n">
-        <v>0.6736</v>
+        <v>0.643</v>
       </c>
       <c r="J88" t="n">
-        <v>15.4928</v>
+        <v>14.789</v>
       </c>
     </row>
     <row r="89">
@@ -4989,10 +4989,10 @@
         <v>1.19</v>
       </c>
       <c r="I89" t="n">
-        <v>0.5506</v>
+        <v>0.5334</v>
       </c>
       <c r="J89" t="n">
-        <v>12.6638</v>
+        <v>12.2682</v>
       </c>
     </row>
     <row r="90">
@@ -5029,10 +5029,10 @@
         <v>1.06</v>
       </c>
       <c r="I90" t="n">
-        <v>0.2021</v>
+        <v>0.2121</v>
       </c>
       <c r="J90" t="n">
-        <v>4.6483</v>
+        <v>4.8783</v>
       </c>
     </row>
     <row r="91">
@@ -5069,10 +5069,10 @@
         <v>0.88</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4414</v>
+        <v>-0.4189</v>
       </c>
       <c r="J91" t="n">
-        <v>-10.1522</v>
+        <v>-9.6347</v>
       </c>
     </row>
     <row r="92">
@@ -5109,10 +5109,10 @@
         <v>1.24</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4587</v>
+        <v>0.5031</v>
       </c>
       <c r="J92" t="n">
-        <v>13.761</v>
+        <v>15.093</v>
       </c>
     </row>
     <row r="93">
@@ -5149,10 +5149,10 @@
         <v>1</v>
       </c>
       <c r="I93" t="n">
-        <v>0.0169</v>
+        <v>0.0121</v>
       </c>
       <c r="J93" t="n">
-        <v>0.507</v>
+        <v>0.363</v>
       </c>
     </row>
     <row r="94">
@@ -5189,10 +5189,10 @@
         <v>0.9</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1253</v>
+        <v>-0.1401</v>
       </c>
       <c r="J94" t="n">
-        <v>-3.759</v>
+        <v>-4.203</v>
       </c>
     </row>
     <row r="95">
@@ -5229,10 +5229,10 @@
         <v>0.82</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2085</v>
+        <v>-0.2244</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.255</v>
+        <v>-6.732</v>
       </c>
     </row>
     <row r="96">
@@ -5269,10 +5269,10 @@
         <v>0.61</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4104</v>
+        <v>-0.4209</v>
       </c>
       <c r="J96" t="n">
-        <v>-12.312</v>
+        <v>-12.627</v>
       </c>
     </row>
     <row r="97">
@@ -5309,10 +5309,10 @@
         <v>1.37</v>
       </c>
       <c r="I97" t="n">
-        <v>0.7655999999999999</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="J97" t="n">
-        <v>22.968</v>
+        <v>24.996</v>
       </c>
     </row>
     <row r="98">
@@ -5349,10 +5349,10 @@
         <v>1.09</v>
       </c>
       <c r="I98" t="n">
-        <v>0.3299</v>
+        <v>0.3244</v>
       </c>
       <c r="J98" t="n">
-        <v>9.897</v>
+        <v>9.731999999999999</v>
       </c>
     </row>
     <row r="99">
@@ -5389,10 +5389,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2199</v>
+        <v>-0.2242</v>
       </c>
       <c r="J99" t="n">
-        <v>-6.597</v>
+        <v>-6.726</v>
       </c>
     </row>
     <row r="100">
@@ -5429,10 +5429,10 @@
         <v>0.93</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2505</v>
+        <v>-0.253</v>
       </c>
       <c r="J100" t="n">
-        <v>-7.515</v>
+        <v>-7.59</v>
       </c>
     </row>
     <row r="101">
@@ -5469,10 +5469,10 @@
         <v>0.49</v>
       </c>
       <c r="I101" t="n">
-        <v>-1.3642</v>
+        <v>-1.2304</v>
       </c>
       <c r="J101" t="n">
-        <v>-40.926</v>
+        <v>-36.912</v>
       </c>
     </row>
     <row r="102">
@@ -5509,10 +5509,10 @@
         <v>0.98</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.0123</v>
+        <v>-0.0245</v>
       </c>
       <c r="J102" t="n">
-        <v>-0.3198</v>
+        <v>-0.637</v>
       </c>
     </row>
     <row r="103">
@@ -5549,10 +5549,10 @@
         <v>0.93</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.07969999999999999</v>
+        <v>-0.096</v>
       </c>
       <c r="J103" t="n">
-        <v>-2.0722</v>
+        <v>-2.496</v>
       </c>
     </row>
     <row r="104">
@@ -5589,10 +5589,10 @@
         <v>0.85</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1689</v>
+        <v>-0.1869</v>
       </c>
       <c r="J104" t="n">
-        <v>-4.3914</v>
+        <v>-4.8594</v>
       </c>
     </row>
     <row r="105">
@@ -5629,10 +5629,10 @@
         <v>0.76</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2561</v>
+        <v>-0.2739</v>
       </c>
       <c r="J105" t="n">
-        <v>-6.6586</v>
+        <v>-7.1214</v>
       </c>
     </row>
     <row r="106">
@@ -5669,10 +5669,10 @@
         <v>0.59</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4171</v>
+        <v>-0.4292</v>
       </c>
       <c r="J106" t="n">
-        <v>-10.8446</v>
+        <v>-11.1592</v>
       </c>
     </row>
     <row r="107">
@@ -5709,10 +5709,10 @@
         <v>1.62</v>
       </c>
       <c r="I107" t="n">
-        <v>1.0272</v>
+        <v>1.1257</v>
       </c>
       <c r="J107" t="n">
-        <v>26.7072</v>
+        <v>29.2682</v>
       </c>
     </row>
     <row r="108">
@@ -5749,10 +5749,10 @@
         <v>1.33</v>
       </c>
       <c r="I108" t="n">
-        <v>0.65</v>
+        <v>0.7198</v>
       </c>
       <c r="J108" t="n">
-        <v>16.9</v>
+        <v>18.7148</v>
       </c>
     </row>
     <row r="109">
@@ -5789,10 +5789,10 @@
         <v>1.2</v>
       </c>
       <c r="I109" t="n">
-        <v>0.4696</v>
+        <v>0.5194</v>
       </c>
       <c r="J109" t="n">
-        <v>12.2096</v>
+        <v>13.5044</v>
       </c>
     </row>
     <row r="110">
@@ -5829,10 +5829,10 @@
         <v>0.98</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1381</v>
+        <v>-0.1302</v>
       </c>
       <c r="J110" t="n">
-        <v>-3.5906</v>
+        <v>-3.3852</v>
       </c>
     </row>
     <row r="111">
@@ -5869,10 +5869,10 @@
         <v>0.74</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.8206</v>
+        <v>-0.755</v>
       </c>
       <c r="J111" t="n">
-        <v>-21.3356</v>
+        <v>-19.63</v>
       </c>
     </row>
     <row r="112">
@@ -5909,10 +5909,10 @@
         <v>1.48</v>
       </c>
       <c r="I112" t="n">
-        <v>0.8797</v>
+        <v>0.9627</v>
       </c>
       <c r="J112" t="n">
-        <v>26.391</v>
+        <v>28.881</v>
       </c>
     </row>
     <row r="113">
@@ -5949,10 +5949,10 @@
         <v>1.23</v>
       </c>
       <c r="I113" t="n">
-        <v>0.5315</v>
+        <v>0.584</v>
       </c>
       <c r="J113" t="n">
-        <v>15.945</v>
+        <v>17.52</v>
       </c>
     </row>
     <row r="114">
@@ -5989,10 +5989,10 @@
         <v>1.05</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1835</v>
+        <v>0.191</v>
       </c>
       <c r="J114" t="n">
-        <v>5.505</v>
+        <v>5.73</v>
       </c>
     </row>
     <row r="115">
@@ -6029,10 +6029,10 @@
         <v>0.8</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.641</v>
+        <v>-0.6012999999999999</v>
       </c>
       <c r="J115" t="n">
-        <v>-19.23</v>
+        <v>-18.039</v>
       </c>
     </row>
     <row r="116">
@@ -6069,10 +6069,10 @@
         <v>0.78</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6926</v>
+        <v>-0.647</v>
       </c>
       <c r="J116" t="n">
-        <v>-20.778</v>
+        <v>-19.41</v>
       </c>
     </row>
     <row r="117">
@@ -6109,10 +6109,10 @@
         <v>1.08</v>
       </c>
       <c r="I117" t="n">
-        <v>0.228</v>
+        <v>0.2292</v>
       </c>
       <c r="J117" t="n">
-        <v>6.84</v>
+        <v>6.876</v>
       </c>
     </row>
     <row r="118">
@@ -6149,10 +6149,10 @@
         <v>1.05</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1602</v>
+        <v>0.163</v>
       </c>
       <c r="J118" t="n">
-        <v>4.806</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="119">
@@ -6189,10 +6189,10 @@
         <v>0.93</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.0929</v>
+        <v>-0.1061</v>
       </c>
       <c r="J119" t="n">
-        <v>-2.787</v>
+        <v>-3.183</v>
       </c>
     </row>
     <row r="120">
@@ -6229,10 +6229,10 @@
         <v>0.85</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1784</v>
+        <v>-0.1941</v>
       </c>
       <c r="J120" t="n">
-        <v>-5.352</v>
+        <v>-5.823</v>
       </c>
     </row>
     <row r="121">
@@ -6269,10 +6269,10 @@
         <v>0.68</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3455</v>
+        <v>-0.3584</v>
       </c>
       <c r="J121" t="n">
-        <v>-10.365</v>
+        <v>-10.752</v>
       </c>
     </row>
     <row r="122">
@@ -6309,10 +6309,10 @@
         <v>1.46</v>
       </c>
       <c r="I122" t="n">
-        <v>0.8162</v>
+        <v>0.9016</v>
       </c>
       <c r="J122" t="n">
-        <v>20.405</v>
+        <v>22.54</v>
       </c>
     </row>
     <row r="123">
@@ -6349,10 +6349,10 @@
         <v>1.44</v>
       </c>
       <c r="I123" t="n">
-        <v>0.7903</v>
+        <v>0.8736</v>
       </c>
       <c r="J123" t="n">
-        <v>19.7575</v>
+        <v>21.84</v>
       </c>
     </row>
     <row r="124">
@@ -6389,10 +6389,10 @@
         <v>1.11</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3277</v>
+        <v>0.336</v>
       </c>
       <c r="J124" t="n">
-        <v>8.192500000000001</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="125">
@@ -6429,10 +6429,10 @@
         <v>1.04</v>
       </c>
       <c r="I125" t="n">
-        <v>0.1192</v>
+        <v>0.1378</v>
       </c>
       <c r="J125" t="n">
-        <v>2.98</v>
+        <v>3.445</v>
       </c>
     </row>
     <row r="126">
@@ -6469,10 +6469,10 @@
         <v>0.95</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.2504</v>
+        <v>-0.2373</v>
       </c>
       <c r="J126" t="n">
-        <v>-6.26</v>
+        <v>-5.9325</v>
       </c>
     </row>
     <row r="127">
@@ -6509,10 +6509,10 @@
         <v>0.98</v>
       </c>
       <c r="I127" t="n">
-        <v>-0.0002</v>
+        <v>-0.0149</v>
       </c>
       <c r="J127" t="n">
-        <v>-0.005</v>
+        <v>-0.3725</v>
       </c>
     </row>
     <row r="128">
@@ -6549,10 +6549,10 @@
         <v>0.77</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.2409</v>
+        <v>-0.2602</v>
       </c>
       <c r="J128" t="n">
-        <v>-6.0225</v>
+        <v>-6.505</v>
       </c>
     </row>
     <row r="129">
@@ -6589,10 +6589,10 @@
         <v>0.74</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2686</v>
+        <v>-0.2875</v>
       </c>
       <c r="J129" t="n">
-        <v>-6.715</v>
+        <v>-7.1875</v>
       </c>
     </row>
     <row r="130">
@@ -6629,10 +6629,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3157</v>
+        <v>-0.3334</v>
       </c>
       <c r="J130" t="n">
-        <v>-7.8925</v>
+        <v>-8.335000000000001</v>
       </c>
     </row>
     <row r="131">
@@ -6669,10 +6669,10 @@
         <v>0.67</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3345</v>
+        <v>-0.3516</v>
       </c>
       <c r="J131" t="n">
-        <v>-8.362500000000001</v>
+        <v>-8.789999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/1886/event_1886_evp_summary.xlsx
+++ b/database/event/1886/event_1886_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.5679</v>
+        <v>4.5955</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1.4552</v>
+        <v>1.4877</v>
       </c>
       <c r="E2" t="n">
-        <v>4.5679</v>
+        <v>4.5955</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4652</v>
+        <v>2.5266</v>
       </c>
       <c r="G2" t="n">
-        <v>2.1027</v>
+        <v>2.0689</v>
       </c>
       <c r="H2" t="n">
-        <v>3.2395</v>
+        <v>3.0434</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7493</v>
+        <v>1.7088</v>
       </c>
       <c r="J2" t="n">
-        <v>2.1027</v>
+        <v>2.0689</v>
       </c>
       <c r="K2" t="n">
         <v>58</v>
@@ -529,7 +529,7 @@
         <v>85</v>
       </c>
       <c r="M2" t="n">
-        <v>3.852</v>
+        <v>3.7777</v>
       </c>
       <c r="N2" t="n">
         <v>143</v>
@@ -538,185 +538,185 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.3731</v>
+        <v>3.2089</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9113</v>
+        <v>0.856</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3731</v>
+        <v>3.2089</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9567</v>
+        <v>2.7568</v>
       </c>
       <c r="G3" t="n">
-        <v>2.4164</v>
+        <v>0.4521</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9567</v>
+        <v>3.9074</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5165999999999999</v>
+        <v>2.1939</v>
       </c>
       <c r="J3" t="n">
-        <v>2.4164</v>
+        <v>0.4521</v>
       </c>
       <c r="K3" t="n">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="L3" t="n">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="M3" t="n">
-        <v>2.933</v>
+        <v>2.646</v>
       </c>
       <c r="N3" t="n">
-        <v>198</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.2292</v>
+        <v>3.1926</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8458</v>
+        <v>0.8486</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2292</v>
+        <v>3.1926</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7506</v>
+        <v>0.8364</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4786</v>
+        <v>2.3562</v>
       </c>
       <c r="H4" t="n">
-        <v>4.1812</v>
+        <v>0.8364</v>
       </c>
       <c r="I4" t="n">
-        <v>2.2578</v>
+        <v>0.4696</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4786</v>
+        <v>2.3562</v>
       </c>
       <c r="K4" t="n">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="L4" t="n">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="M4" t="n">
-        <v>2.7364</v>
+        <v>2.8258</v>
       </c>
       <c r="N4" t="n">
-        <v>188</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.7951</v>
+        <v>2.8639</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6482</v>
+        <v>0.6989</v>
       </c>
       <c r="E5" t="n">
-        <v>2.7951</v>
+        <v>2.8639</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4635</v>
+        <v>2.5112</v>
       </c>
       <c r="G5" t="n">
-        <v>2.3316</v>
+        <v>0.3527</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4635</v>
+        <v>2.9854</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2503</v>
+        <v>1.6762</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3316</v>
+        <v>0.3527</v>
       </c>
       <c r="K5" t="n">
-        <v>114</v>
+        <v>58</v>
       </c>
       <c r="L5" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M5" t="n">
-        <v>2.5819</v>
+        <v>2.0289</v>
       </c>
       <c r="N5" t="n">
-        <v>198</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.7655</v>
+        <v>2.4993</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6347</v>
+        <v>0.5328000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7655</v>
+        <v>2.4993</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4376</v>
+        <v>0.3076</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3279</v>
+        <v>2.1917</v>
       </c>
       <c r="H6" t="n">
-        <v>3.1482</v>
+        <v>0.3076</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7</v>
+        <v>0.1727</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3279</v>
+        <v>2.1917</v>
       </c>
       <c r="K6" t="n">
-        <v>58</v>
+        <v>114</v>
       </c>
       <c r="L6" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M6" t="n">
-        <v>2.0279</v>
+        <v>2.3644</v>
       </c>
       <c r="N6" t="n">
-        <v>143</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7">
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.257</v>
+        <v>2.2956</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4032</v>
+        <v>0.44</v>
       </c>
       <c r="E7" t="n">
-        <v>2.257</v>
+        <v>2.2956</v>
       </c>
       <c r="F7" t="n">
-        <v>2.5774</v>
+        <v>2.5823</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3204</v>
+        <v>-0.2867</v>
       </c>
       <c r="H7" t="n">
-        <v>3.6097</v>
+        <v>3.2524</v>
       </c>
       <c r="I7" t="n">
-        <v>1.9492</v>
+        <v>1.8261</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3204</v>
+        <v>-0.2867</v>
       </c>
       <c r="K7" t="n">
         <v>132</v>
@@ -759,7 +759,7 @@
         <v>56</v>
       </c>
       <c r="M7" t="n">
-        <v>1.6288</v>
+        <v>1.5394</v>
       </c>
       <c r="N7" t="n">
         <v>188</v>
@@ -768,93 +768,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Hiko</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7658</v>
+        <v>0.7234</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2756</v>
+        <v>-0.2762</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7658</v>
+        <v>0.7234</v>
       </c>
       <c r="F8" t="n">
-        <v>0.863</v>
+        <v>-1.2425</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.09719999999999999</v>
+        <v>1.9659</v>
       </c>
       <c r="H8" t="n">
-        <v>0.863</v>
+        <v>-1.2425</v>
       </c>
       <c r="I8" t="n">
-        <v>0.466</v>
+        <v>-0.6976</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.09719999999999999</v>
+        <v>1.9659</v>
       </c>
       <c r="K8" t="n">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="L8" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3688</v>
+        <v>1.2683</v>
       </c>
       <c r="N8" t="n">
-        <v>131</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>Hiko</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5598</v>
+        <v>0.5524</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3694</v>
+        <v>-0.3541</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5598</v>
+        <v>0.5524</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4193</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>1.9791</v>
+        <v>-0.1175</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.4193</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7664</v>
+        <v>0.3761</v>
       </c>
       <c r="J9" t="n">
-        <v>1.9791</v>
+        <v>-0.1175</v>
       </c>
       <c r="K9" t="n">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="L9" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="M9" t="n">
-        <v>1.2127</v>
+        <v>0.2586</v>
       </c>
       <c r="N9" t="n">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10">
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4822</v>
+        <v>0.442</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4047</v>
+        <v>-0.4044</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4822</v>
+        <v>0.442</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2783</v>
+        <v>0.3208</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2039</v>
+        <v>0.1212</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2783</v>
+        <v>0.3208</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1503</v>
+        <v>0.1801</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2039</v>
+        <v>0.1212</v>
       </c>
       <c r="K10" t="n">
         <v>114</v>
@@ -897,7 +897,7 @@
         <v>84</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3542</v>
+        <v>0.3013</v>
       </c>
       <c r="N10" t="n">
         <v>198</v>
@@ -906,93 +906,93 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2835</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4951</v>
+        <v>-0.5684</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2835</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8528</v>
+        <v>1.3837</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5693</v>
+        <v>-1.3016</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8528</v>
+        <v>1.3837</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4605</v>
+        <v>0.7769</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5693</v>
+        <v>-1.3016</v>
       </c>
       <c r="K11" t="n">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="L11" t="n">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1088</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>188</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0704</v>
+        <v>0.0694</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.5921999999999999</v>
+        <v>-0.5742</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0704</v>
+        <v>0.0694</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4767</v>
+        <v>0.612</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.4063</v>
+        <v>-0.5426</v>
       </c>
       <c r="H12" t="n">
-        <v>1.4767</v>
+        <v>0.612</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7974</v>
+        <v>0.3436</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.4063</v>
+        <v>-0.5426</v>
       </c>
       <c r="K12" t="n">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="L12" t="n">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.6089000000000001</v>
+        <v>-0.199</v>
       </c>
       <c r="N12" t="n">
-        <v>198</v>
+        <v>188</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.2648</v>
+        <v>-0.3846</v>
       </c>
       <c r="C13" t="n">
         <v>-0</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.7447</v>
+        <v>-0.781</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.2648</v>
+        <v>-0.3846</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1606</v>
+        <v>-0.2513</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1042</v>
+        <v>-0.1333</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1606</v>
+        <v>-0.2513</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0867</v>
+        <v>-0.1411</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.1042</v>
+        <v>-0.1333</v>
       </c>
       <c r="K13" t="n">
         <v>76</v>
@@ -1035,7 +1035,7 @@
         <v>55</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.1909</v>
+        <v>-0.2744</v>
       </c>
       <c r="N13" t="n">
         <v>131</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.4398</v>
+        <v>-0.4703</v>
       </c>
       <c r="C14" t="n">
         <v>-0</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.8244</v>
+        <v>-0.82</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.4398</v>
+        <v>-0.4703</v>
       </c>
       <c r="F14" t="n">
-        <v>0.062</v>
+        <v>0.0689</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.5018</v>
+        <v>-0.5392</v>
       </c>
       <c r="H14" t="n">
-        <v>0.062</v>
+        <v>0.0689</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0335</v>
+        <v>0.0387</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.5018</v>
+        <v>-0.5392</v>
       </c>
       <c r="K14" t="n">
         <v>58</v>
@@ -1081,7 +1081,7 @@
         <v>85</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4683</v>
+        <v>-0.5005000000000001</v>
       </c>
       <c r="N14" t="n">
         <v>143</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-1.0501</v>
+        <v>-1.0209</v>
       </c>
       <c r="C15" t="n">
         <v>-0</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.1022</v>
+        <v>-1.0709</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.0501</v>
+        <v>-1.0209</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9291</v>
+        <v>-0.9238</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.121</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.9291</v>
+        <v>-0.9238</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5017</v>
+        <v>-0.5187</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.121</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="K15" t="n">
         <v>76</v>
@@ -1127,7 +1127,7 @@
         <v>55</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6227</v>
+        <v>-0.6158</v>
       </c>
       <c r="N15" t="n">
         <v>131</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-1.0672</v>
+        <v>-1.036</v>
       </c>
       <c r="C16" t="n">
         <v>-0</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.11</v>
+        <v>-1.0777</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.0672</v>
+        <v>-1.036</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8924</v>
+        <v>-0.8743</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1748</v>
+        <v>-0.1617</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8924</v>
+        <v>-0.8743</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4819</v>
+        <v>-0.4909</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1748</v>
+        <v>-0.1617</v>
       </c>
       <c r="K16" t="n">
         <v>132</v>
@@ -1173,7 +1173,7 @@
         <v>56</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6567000000000001</v>
+        <v>-0.6526000000000001</v>
       </c>
       <c r="N16" t="n">
         <v>188</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-1.196</v>
+        <v>-1.124</v>
       </c>
       <c r="C17" t="n">
         <v>-0</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.1686</v>
+        <v>-1.1178</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.196</v>
+        <v>-1.124</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3902</v>
+        <v>-0.3245</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8058</v>
+        <v>-0.7995</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3902</v>
+        <v>-0.3245</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2107</v>
+        <v>-0.1822</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.8058</v>
+        <v>-0.7995</v>
       </c>
       <c r="K17" t="n">
         <v>58</v>
@@ -1219,7 +1219,7 @@
         <v>85</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0165</v>
+        <v>-0.9817</v>
       </c>
       <c r="N17" t="n">
         <v>143</v>
@@ -1228,81 +1228,81 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>adreN</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-1.3348</v>
+        <v>-1.276</v>
       </c>
       <c r="C18" t="n">
         <v>-0</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2318</v>
+        <v>-1.1871</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3348</v>
+        <v>-1.276</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7891</v>
+        <v>-0.2529</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5457</v>
+        <v>-1.0231</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7891</v>
+        <v>-0.2529</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4261</v>
+        <v>-0.142</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5457</v>
+        <v>-1.0231</v>
       </c>
       <c r="K18" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="L18" t="n">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9718</v>
+        <v>-1.1651</v>
       </c>
       <c r="N18" t="n">
-        <v>131</v>
+        <v>198</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>adreN</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-1.3426</v>
+        <v>-1.3096</v>
       </c>
       <c r="C19" t="n">
         <v>-0</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2354</v>
+        <v>-1.2024</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3426</v>
+        <v>-1.3096</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6967</v>
+        <v>-0.7984</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6459</v>
+        <v>-0.5112</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6967</v>
+        <v>-0.7984</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3762</v>
+        <v>-0.4483</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6459</v>
+        <v>-0.5112</v>
       </c>
       <c r="K19" t="n">
         <v>76</v>
@@ -1311,7 +1311,7 @@
         <v>55</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0221</v>
+        <v>-0.9595</v>
       </c>
       <c r="N19" t="n">
         <v>131</v>
@@ -1320,47 +1320,47 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-1.3929</v>
+        <v>-1.3098</v>
       </c>
       <c r="C20" t="n">
         <v>-0</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2583</v>
+        <v>-1.2025</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3929</v>
+        <v>-1.3098</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3619</v>
+        <v>-0.695</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.031</v>
+        <v>-0.6148</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3619</v>
+        <v>-0.695</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1954</v>
+        <v>-0.3902</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.031</v>
+        <v>-0.6148</v>
       </c>
       <c r="K20" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="L20" t="n">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2264</v>
+        <v>-1.005</v>
       </c>
       <c r="N20" t="n">
-        <v>198</v>
+        <v>131</v>
       </c>
     </row>
     <row r="21">
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-3.255</v>
+        <v>-3.0601</v>
       </c>
       <c r="C21" t="n">
         <v>-0</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1059</v>
+        <v>-1.9998</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.255</v>
+        <v>-3.0601</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.5602</v>
+        <v>-2.3923</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6948</v>
+        <v>-0.6677999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.5602</v>
+        <v>-2.3923</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.3825</v>
+        <v>-1.3432</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6948</v>
+        <v>-0.6677999999999999</v>
       </c>
       <c r="K21" t="n">
         <v>132</v>
@@ -1403,7 +1403,7 @@
         <v>56</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.0773</v>
+        <v>-2.011</v>
       </c>
       <c r="N21" t="n">
         <v>188</v>
@@ -1509,10 +1509,10 @@
         <v>1.34</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8433</v>
+        <v>0.8207</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8433</v>
+        <v>0.8207</v>
       </c>
     </row>
     <row r="3">
@@ -1549,10 +1549,10 @@
         <v>1.27</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7002</v>
+        <v>0.6686</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7002</v>
+        <v>0.6686</v>
       </c>
     </row>
     <row r="4">
@@ -1589,10 +1589,10 @@
         <v>1.26</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6792</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6792</v>
+        <v>0.6467000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -1629,10 +1629,10 @@
         <v>1.17</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4839</v>
+        <v>0.447</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4839</v>
+        <v>0.447</v>
       </c>
     </row>
     <row r="6">
@@ -1669,10 +1669,10 @@
         <v>0.74</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.752</v>
+        <v>-0.7261</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.752</v>
+        <v>-0.7261</v>
       </c>
     </row>
     <row r="7">
@@ -1709,10 +1709,10 @@
         <v>1.18</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4269</v>
+        <v>0.3718</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4269</v>
+        <v>0.3718</v>
       </c>
     </row>
     <row r="8">
@@ -1749,10 +1749,10 @@
         <v>0.88</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1608</v>
+        <v>-0.1423</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1608</v>
+        <v>-0.1423</v>
       </c>
     </row>
     <row r="9">
@@ -1789,10 +1789,10 @@
         <v>0.87</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1714</v>
+        <v>-0.1525</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1714</v>
+        <v>-0.1525</v>
       </c>
     </row>
     <row r="10">
@@ -1829,10 +1829,10 @@
         <v>0.87</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1714</v>
+        <v>-0.1525</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1714</v>
+        <v>-0.1525</v>
       </c>
     </row>
     <row r="11">
@@ -1869,10 +1869,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3472</v>
+        <v>-0.3318</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3472</v>
+        <v>-0.3318</v>
       </c>
     </row>
     <row r="12">
@@ -1909,10 +1909,10 @@
         <v>1.4</v>
       </c>
       <c r="I12" t="n">
-        <v>1.0047</v>
+        <v>0.9997</v>
       </c>
       <c r="J12" t="n">
-        <v>28.1316</v>
+        <v>27.9916</v>
       </c>
     </row>
     <row r="13">
@@ -1949,10 +1949,10 @@
         <v>1.12</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3867</v>
+        <v>0.3447</v>
       </c>
       <c r="J13" t="n">
-        <v>10.8276</v>
+        <v>9.6516</v>
       </c>
     </row>
     <row r="14">
@@ -1989,10 +1989,10 @@
         <v>0.92</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2935</v>
+        <v>-0.2528</v>
       </c>
       <c r="J14" t="n">
-        <v>-8.218</v>
+        <v>-7.0784</v>
       </c>
     </row>
     <row r="15">
@@ -2029,10 +2029,10 @@
         <v>0.86</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4505</v>
+        <v>-0.4075</v>
       </c>
       <c r="J15" t="n">
-        <v>-12.614</v>
+        <v>-11.41</v>
       </c>
     </row>
     <row r="16">
@@ -2069,10 +2069,10 @@
         <v>0.85</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4751</v>
+        <v>-0.4325</v>
       </c>
       <c r="J16" t="n">
-        <v>-13.3028</v>
+        <v>-12.11</v>
       </c>
     </row>
     <row r="17">
@@ -2109,10 +2109,10 @@
         <v>1.37</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7235</v>
+        <v>0.6709000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>20.258</v>
+        <v>18.7852</v>
       </c>
     </row>
     <row r="18">
@@ -2149,10 +2149,10 @@
         <v>1.2</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4471</v>
+        <v>0.3899</v>
       </c>
       <c r="J18" t="n">
-        <v>12.5188</v>
+        <v>10.9172</v>
       </c>
     </row>
     <row r="19">
@@ -2189,10 +2189,10 @@
         <v>1.08</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2223</v>
+        <v>0.1784</v>
       </c>
       <c r="J19" t="n">
-        <v>6.2244</v>
+        <v>4.9952</v>
       </c>
     </row>
     <row r="20">
@@ -2229,10 +2229,10 @@
         <v>0.68</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3612</v>
+        <v>-0.3471</v>
       </c>
       <c r="J20" t="n">
-        <v>-10.1136</v>
+        <v>-9.7188</v>
       </c>
     </row>
     <row r="21">
@@ -2269,10 +2269,10 @@
         <v>0.41</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5943000000000001</v>
+        <v>-0.6099</v>
       </c>
       <c r="J21" t="n">
-        <v>-16.6404</v>
+        <v>-17.0772</v>
       </c>
     </row>
     <row r="22">
@@ -2309,10 +2309,10 @@
         <v>1.07</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2321</v>
+        <v>0.1903</v>
       </c>
       <c r="J22" t="n">
-        <v>6.4988</v>
+        <v>5.3284</v>
       </c>
     </row>
     <row r="23">
@@ -2349,10 +2349,10 @@
         <v>1.02</v>
       </c>
       <c r="I23" t="n">
-        <v>0.108</v>
+        <v>0.0822</v>
       </c>
       <c r="J23" t="n">
-        <v>3.024</v>
+        <v>2.3016</v>
       </c>
     </row>
     <row r="24">
@@ -2389,10 +2389,10 @@
         <v>0.89</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1448</v>
+        <v>-0.1288</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.0544</v>
+        <v>-3.6064</v>
       </c>
     </row>
     <row r="25">
@@ -2429,10 +2429,10 @@
         <v>0.8</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2366</v>
+        <v>-0.2181</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.6248</v>
+        <v>-6.1068</v>
       </c>
     </row>
     <row r="26">
@@ -2469,10 +2469,10 @@
         <v>0.38</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6107</v>
+        <v>-0.6274</v>
       </c>
       <c r="J26" t="n">
-        <v>-17.0996</v>
+        <v>-17.5672</v>
       </c>
     </row>
     <row r="27">
@@ -2509,10 +2509,10 @@
         <v>1.35</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8569</v>
+        <v>0.8359</v>
       </c>
       <c r="J27" t="n">
-        <v>23.9932</v>
+        <v>23.4052</v>
       </c>
     </row>
     <row r="28">
@@ -2549,10 +2549,10 @@
         <v>1.32</v>
       </c>
       <c r="I28" t="n">
-        <v>0.797</v>
+        <v>0.7718</v>
       </c>
       <c r="J28" t="n">
-        <v>22.316</v>
+        <v>21.6104</v>
       </c>
     </row>
     <row r="29">
@@ -2589,10 +2589,10 @@
         <v>1.22</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5899</v>
+        <v>0.5556</v>
       </c>
       <c r="J29" t="n">
-        <v>16.5172</v>
+        <v>15.5568</v>
       </c>
     </row>
     <row r="30">
@@ -2629,10 +2629,10 @@
         <v>1.2</v>
       </c>
       <c r="I30" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.5118</v>
       </c>
       <c r="J30" t="n">
-        <v>15.3132</v>
+        <v>14.3304</v>
       </c>
     </row>
     <row r="31">
@@ -2669,10 +2669,10 @@
         <v>0.82</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5759</v>
+        <v>-0.5389</v>
       </c>
       <c r="J31" t="n">
-        <v>-16.1252</v>
+        <v>-15.0892</v>
       </c>
     </row>
     <row r="32">
@@ -2709,10 +2709,10 @@
         <v>1.44</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8074</v>
+        <v>0.7559</v>
       </c>
       <c r="J32" t="n">
-        <v>22.6072</v>
+        <v>21.1652</v>
       </c>
     </row>
     <row r="33">
@@ -2749,10 +2749,10 @@
         <v>1.26</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5308</v>
+        <v>0.4714</v>
       </c>
       <c r="J33" t="n">
-        <v>14.8624</v>
+        <v>13.1992</v>
       </c>
     </row>
     <row r="34">
@@ -2789,10 +2789,10 @@
         <v>1.05</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1465</v>
+        <v>0.1129</v>
       </c>
       <c r="J34" t="n">
-        <v>4.102</v>
+        <v>3.1612</v>
       </c>
     </row>
     <row r="35">
@@ -2829,10 +2829,10 @@
         <v>0.92</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1245</v>
+        <v>-0.1058</v>
       </c>
       <c r="J35" t="n">
-        <v>-3.486</v>
+        <v>-2.9624</v>
       </c>
     </row>
     <row r="36">
@@ -2869,10 +2869,10 @@
         <v>0.38</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6227</v>
+        <v>-0.6442</v>
       </c>
       <c r="J36" t="n">
-        <v>-17.4356</v>
+        <v>-18.0376</v>
       </c>
     </row>
     <row r="37">
@@ -2909,10 +2909,10 @@
         <v>1.33</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8735000000000001</v>
+        <v>0.8552999999999999</v>
       </c>
       <c r="J37" t="n">
-        <v>24.458</v>
+        <v>23.9484</v>
       </c>
     </row>
     <row r="38">
@@ -2949,10 +2949,10 @@
         <v>1.18</v>
       </c>
       <c r="I38" t="n">
-        <v>0.5414</v>
+        <v>0.5003</v>
       </c>
       <c r="J38" t="n">
-        <v>15.1592</v>
+        <v>14.0084</v>
       </c>
     </row>
     <row r="39">
@@ -2989,10 +2989,10 @@
         <v>0.92</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.2873</v>
+        <v>-0.2474</v>
       </c>
       <c r="J39" t="n">
-        <v>-8.0444</v>
+        <v>-6.9272</v>
       </c>
     </row>
     <row r="40">
@@ -3029,10 +3029,10 @@
         <v>0.8</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.587</v>
+        <v>-0.5476</v>
       </c>
       <c r="J40" t="n">
-        <v>-16.436</v>
+        <v>-15.3328</v>
       </c>
     </row>
     <row r="41">
@@ -3069,10 +3069,10 @@
         <v>0.76</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6777</v>
+        <v>-0.6431</v>
       </c>
       <c r="J41" t="n">
-        <v>-18.9756</v>
+        <v>-18.0068</v>
       </c>
     </row>
     <row r="42">
@@ -3109,10 +3109,10 @@
         <v>1.34</v>
       </c>
       <c r="I42" t="n">
-        <v>0.6673</v>
+        <v>0.6109</v>
       </c>
       <c r="J42" t="n">
-        <v>18.6844</v>
+        <v>17.1052</v>
       </c>
     </row>
     <row r="43">
@@ -3149,10 +3149,10 @@
         <v>1.05</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1516</v>
+        <v>0.1166</v>
       </c>
       <c r="J43" t="n">
-        <v>4.2448</v>
+        <v>3.2648</v>
       </c>
     </row>
     <row r="44">
@@ -3189,10 +3189,10 @@
         <v>0.98</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.0416</v>
+        <v>-0.0319</v>
       </c>
       <c r="J44" t="n">
-        <v>-1.1648</v>
+        <v>-0.8932</v>
       </c>
     </row>
     <row r="45">
@@ -3229,10 +3229,10 @@
         <v>0.91</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1334</v>
+        <v>-0.1146</v>
       </c>
       <c r="J45" t="n">
-        <v>-3.7352</v>
+        <v>-3.2088</v>
       </c>
     </row>
     <row r="46">
@@ -3269,10 +3269,10 @@
         <v>0.6</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4352</v>
+        <v>-0.4285</v>
       </c>
       <c r="J46" t="n">
-        <v>-12.1856</v>
+        <v>-11.998</v>
       </c>
     </row>
     <row r="47">
@@ -3309,10 +3309,10 @@
         <v>1.48</v>
       </c>
       <c r="I47" t="n">
-        <v>1.1019</v>
+        <v>1.1145</v>
       </c>
       <c r="J47" t="n">
-        <v>30.8532</v>
+        <v>31.206</v>
       </c>
     </row>
     <row r="48">
@@ -3349,10 +3349,10 @@
         <v>1.36</v>
       </c>
       <c r="I48" t="n">
-        <v>0.9003</v>
+        <v>0.8823</v>
       </c>
       <c r="J48" t="n">
-        <v>25.2084</v>
+        <v>24.7044</v>
       </c>
     </row>
     <row r="49">
@@ -3389,10 +3389,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2486</v>
+        <v>-0.2098</v>
       </c>
       <c r="J49" t="n">
-        <v>-6.9608</v>
+        <v>-5.8744</v>
       </c>
     </row>
     <row r="50">
@@ -3429,10 +3429,10 @@
         <v>0.9</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.361</v>
+        <v>-0.3184</v>
       </c>
       <c r="J50" t="n">
-        <v>-10.108</v>
+        <v>-8.9152</v>
       </c>
     </row>
     <row r="51">
@@ -3469,10 +3469,10 @@
         <v>0.8</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6068</v>
+        <v>-0.5695</v>
       </c>
       <c r="J51" t="n">
-        <v>-16.9904</v>
+        <v>-15.946</v>
       </c>
     </row>
     <row r="52">
@@ -3509,10 +3509,10 @@
         <v>1.07</v>
       </c>
       <c r="I52" t="n">
-        <v>0.2295</v>
+        <v>0.1874</v>
       </c>
       <c r="J52" t="n">
-        <v>6.885</v>
+        <v>5.622</v>
       </c>
     </row>
     <row r="53">
@@ -3549,10 +3549,10 @@
         <v>0.92</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1107</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="J53" t="n">
-        <v>-3.321</v>
+        <v>-2.886</v>
       </c>
     </row>
     <row r="54">
@@ -3589,10 +3589,10 @@
         <v>0.87</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1675</v>
+        <v>-0.1504</v>
       </c>
       <c r="J54" t="n">
-        <v>-5.025</v>
+        <v>-4.512</v>
       </c>
     </row>
     <row r="55">
@@ -3629,10 +3629,10 @@
         <v>0.7</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3319</v>
+        <v>-0.3157</v>
       </c>
       <c r="J55" t="n">
-        <v>-9.957000000000001</v>
+        <v>-9.471</v>
       </c>
     </row>
     <row r="56">
@@ -3669,10 +3669,10 @@
         <v>0.64</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3866</v>
+        <v>-0.374</v>
       </c>
       <c r="J56" t="n">
-        <v>-11.598</v>
+        <v>-11.22</v>
       </c>
     </row>
     <row r="57">
@@ -3709,10 +3709,10 @@
         <v>1.34</v>
       </c>
       <c r="I57" t="n">
-        <v>0.849</v>
+        <v>0.8265</v>
       </c>
       <c r="J57" t="n">
-        <v>25.47</v>
+        <v>24.795</v>
       </c>
     </row>
     <row r="58">
@@ -3749,10 +3749,10 @@
         <v>1.22</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5981</v>
+        <v>0.5617</v>
       </c>
       <c r="J58" t="n">
-        <v>17.943</v>
+        <v>16.851</v>
       </c>
     </row>
     <row r="59">
@@ -3789,10 +3789,10 @@
         <v>1.13</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3945</v>
+        <v>0.3571</v>
       </c>
       <c r="J59" t="n">
-        <v>11.835</v>
+        <v>10.713</v>
       </c>
     </row>
     <row r="60">
@@ -3829,10 +3829,10 @@
         <v>1.01</v>
       </c>
       <c r="I60" t="n">
-        <v>0.0379</v>
+        <v>0.0276</v>
       </c>
       <c r="J60" t="n">
-        <v>1.137</v>
+        <v>0.828</v>
       </c>
     </row>
     <row r="61">
@@ -3869,10 +3869,10 @@
         <v>0.97</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.1596</v>
+        <v>-0.1281</v>
       </c>
       <c r="J61" t="n">
-        <v>-4.788</v>
+        <v>-3.843</v>
       </c>
     </row>
     <row r="62">
@@ -3909,10 +3909,10 @@
         <v>1.17</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4421</v>
+        <v>0.3931</v>
       </c>
       <c r="J62" t="n">
-        <v>11.0525</v>
+        <v>9.827500000000001</v>
       </c>
     </row>
     <row r="63">
@@ -3949,10 +3949,10 @@
         <v>1.08</v>
       </c>
       <c r="I63" t="n">
-        <v>0.2624</v>
+        <v>0.2198</v>
       </c>
       <c r="J63" t="n">
-        <v>6.56</v>
+        <v>5.495</v>
       </c>
     </row>
     <row r="64">
@@ -3989,10 +3989,10 @@
         <v>0.83</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.2059</v>
+        <v>-0.1887</v>
       </c>
       <c r="J64" t="n">
-        <v>-5.1475</v>
+        <v>-4.7175</v>
       </c>
     </row>
     <row r="65">
@@ -4029,10 +4029,10 @@
         <v>0.51</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.4977</v>
+        <v>-0.4967</v>
       </c>
       <c r="J65" t="n">
-        <v>-12.4425</v>
+        <v>-12.4175</v>
       </c>
     </row>
     <row r="66">
@@ -4069,10 +4069,10 @@
         <v>0.45</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5494</v>
+        <v>-0.5556</v>
       </c>
       <c r="J66" t="n">
-        <v>-13.735</v>
+        <v>-13.89</v>
       </c>
     </row>
     <row r="67">
@@ -4109,10 +4109,10 @@
         <v>1.45</v>
       </c>
       <c r="I67" t="n">
-        <v>1.0414</v>
+        <v>1.0454</v>
       </c>
       <c r="J67" t="n">
-        <v>26.035</v>
+        <v>26.135</v>
       </c>
     </row>
     <row r="68">
@@ -4149,10 +4149,10 @@
         <v>1.38</v>
       </c>
       <c r="I68" t="n">
-        <v>0.9207</v>
+        <v>0.9051</v>
       </c>
       <c r="J68" t="n">
-        <v>23.0175</v>
+        <v>22.6275</v>
       </c>
     </row>
     <row r="69">
@@ -4189,10 +4189,10 @@
         <v>1.14</v>
       </c>
       <c r="I69" t="n">
-        <v>0.4151</v>
+        <v>0.3789</v>
       </c>
       <c r="J69" t="n">
-        <v>10.3775</v>
+        <v>9.4725</v>
       </c>
     </row>
     <row r="70">
@@ -4229,10 +4229,10 @@
         <v>1.03</v>
       </c>
       <c r="I70" t="n">
-        <v>0.1108</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="J70" t="n">
-        <v>2.77</v>
+        <v>2.2475</v>
       </c>
     </row>
     <row r="71">
@@ -4269,10 +4269,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5957</v>
+        <v>-0.5593</v>
       </c>
       <c r="J71" t="n">
-        <v>-14.8925</v>
+        <v>-13.9825</v>
       </c>
     </row>
     <row r="72">
@@ -4309,10 +4309,10 @@
         <v>1.48</v>
       </c>
       <c r="I72" t="n">
-        <v>0.6194</v>
+        <v>0.5484</v>
       </c>
       <c r="J72" t="n">
-        <v>17.3432</v>
+        <v>15.3552</v>
       </c>
     </row>
     <row r="73">
@@ -4349,10 +4349,10 @@
         <v>1.21</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3181</v>
+        <v>0.2617</v>
       </c>
       <c r="J73" t="n">
-        <v>8.9068</v>
+        <v>7.3276</v>
       </c>
     </row>
     <row r="74">
@@ -4389,10 +4389,10 @@
         <v>1.1</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1771</v>
+        <v>0.1383</v>
       </c>
       <c r="J74" t="n">
-        <v>4.9588</v>
+        <v>3.8724</v>
       </c>
     </row>
     <row r="75">
@@ -4429,10 +4429,10 @@
         <v>0.93</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.1211</v>
+        <v>-0.1025</v>
       </c>
       <c r="J75" t="n">
-        <v>-3.3908</v>
+        <v>-2.87</v>
       </c>
     </row>
     <row r="76">
@@ -4469,10 +4469,10 @@
         <v>0.86</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.2009</v>
+        <v>-0.1805</v>
       </c>
       <c r="J76" t="n">
-        <v>-5.6252</v>
+        <v>-5.054</v>
       </c>
     </row>
     <row r="77">
@@ -4509,10 +4509,10 @@
         <v>1.17</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3417</v>
+        <v>0.3393</v>
       </c>
       <c r="J77" t="n">
-        <v>9.567600000000001</v>
+        <v>9.500400000000001</v>
       </c>
     </row>
     <row r="78">
@@ -4549,10 +4549,10 @@
         <v>0.89</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.1437</v>
+        <v>-0.1278</v>
       </c>
       <c r="J78" t="n">
-        <v>-4.0236</v>
+        <v>-3.5784</v>
       </c>
     </row>
     <row r="79">
@@ -4589,10 +4589,10 @@
         <v>0.83</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.207</v>
+        <v>-0.1893</v>
       </c>
       <c r="J79" t="n">
-        <v>-5.796</v>
+        <v>-5.3004</v>
       </c>
     </row>
     <row r="80">
@@ -4629,10 +4629,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3392</v>
+        <v>-0.3234</v>
       </c>
       <c r="J80" t="n">
-        <v>-9.4976</v>
+        <v>-9.055199999999999</v>
       </c>
     </row>
     <row r="81">
@@ -4669,10 +4669,10 @@
         <v>0.53</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4818</v>
+        <v>-0.4789</v>
       </c>
       <c r="J81" t="n">
-        <v>-13.4904</v>
+        <v>-13.4092</v>
       </c>
     </row>
     <row r="82">
@@ -4709,10 +4709,10 @@
         <v>1.06</v>
       </c>
       <c r="I82" t="n">
-        <v>0.2444</v>
+        <v>0.2098</v>
       </c>
       <c r="J82" t="n">
-        <v>5.6212</v>
+        <v>4.8254</v>
       </c>
     </row>
     <row r="83">
@@ -4749,10 +4749,10 @@
         <v>0.82</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.2084</v>
+        <v>-0.1928</v>
       </c>
       <c r="J83" t="n">
-        <v>-4.7932</v>
+        <v>-4.4344</v>
       </c>
     </row>
     <row r="84">
@@ -4789,10 +4789,10 @@
         <v>0.73</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.2942</v>
+        <v>-0.2787</v>
       </c>
       <c r="J84" t="n">
-        <v>-6.7666</v>
+        <v>-6.4101</v>
       </c>
     </row>
     <row r="85">
@@ -4829,10 +4829,10 @@
         <v>0.57</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.4377</v>
+        <v>-0.4295</v>
       </c>
       <c r="J85" t="n">
-        <v>-10.0671</v>
+        <v>-9.878500000000001</v>
       </c>
     </row>
     <row r="86">
@@ -4869,10 +4869,10 @@
         <v>0.53</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4729</v>
+        <v>-0.4683</v>
       </c>
       <c r="J86" t="n">
-        <v>-10.8767</v>
+        <v>-10.7709</v>
       </c>
     </row>
     <row r="87">
@@ -4909,10 +4909,10 @@
         <v>1.26</v>
       </c>
       <c r="I87" t="n">
-        <v>0.6857</v>
+        <v>0.6525</v>
       </c>
       <c r="J87" t="n">
-        <v>15.7711</v>
+        <v>15.0075</v>
       </c>
     </row>
     <row r="88">
@@ -4949,10 +4949,10 @@
         <v>1.24</v>
       </c>
       <c r="I88" t="n">
-        <v>0.643</v>
+        <v>0.6079</v>
       </c>
       <c r="J88" t="n">
-        <v>14.789</v>
+        <v>13.9817</v>
       </c>
     </row>
     <row r="89">
@@ -4989,10 +4989,10 @@
         <v>1.19</v>
       </c>
       <c r="I89" t="n">
-        <v>0.5334</v>
+        <v>0.4952</v>
       </c>
       <c r="J89" t="n">
-        <v>12.2682</v>
+        <v>11.3896</v>
       </c>
     </row>
     <row r="90">
@@ -5029,10 +5029,10 @@
         <v>1.06</v>
       </c>
       <c r="I90" t="n">
-        <v>0.2121</v>
+        <v>0.1821</v>
       </c>
       <c r="J90" t="n">
-        <v>4.8783</v>
+        <v>4.1883</v>
       </c>
     </row>
     <row r="91">
@@ -5069,10 +5069,10 @@
         <v>0.88</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4189</v>
+        <v>-0.3765</v>
       </c>
       <c r="J91" t="n">
-        <v>-9.6347</v>
+        <v>-8.6595</v>
       </c>
     </row>
     <row r="92">
@@ -5109,10 +5109,10 @@
         <v>1.24</v>
       </c>
       <c r="I92" t="n">
-        <v>0.5031</v>
+        <v>0.4693</v>
       </c>
       <c r="J92" t="n">
-        <v>15.093</v>
+        <v>14.079</v>
       </c>
     </row>
     <row r="93">
@@ -5149,10 +5149,10 @@
         <v>1</v>
       </c>
       <c r="I93" t="n">
-        <v>0.0121</v>
+        <v>0.008</v>
       </c>
       <c r="J93" t="n">
-        <v>0.363</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="94">
@@ -5189,10 +5189,10 @@
         <v>0.9</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1401</v>
+        <v>-0.1222</v>
       </c>
       <c r="J94" t="n">
-        <v>-4.203</v>
+        <v>-3.666</v>
       </c>
     </row>
     <row r="95">
@@ -5229,10 +5229,10 @@
         <v>0.82</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2244</v>
+        <v>-0.2044</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.732</v>
+        <v>-6.132</v>
       </c>
     </row>
     <row r="96">
@@ -5269,10 +5269,10 @@
         <v>0.61</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4209</v>
+        <v>-0.4119</v>
       </c>
       <c r="J96" t="n">
-        <v>-12.627</v>
+        <v>-12.357</v>
       </c>
     </row>
     <row r="97">
@@ -5309,10 +5309,10 @@
         <v>1.37</v>
       </c>
       <c r="I97" t="n">
-        <v>0.8332000000000001</v>
+        <v>0.8215</v>
       </c>
       <c r="J97" t="n">
-        <v>24.996</v>
+        <v>24.645</v>
       </c>
     </row>
     <row r="98">
@@ -5349,10 +5349,10 @@
         <v>1.09</v>
       </c>
       <c r="I98" t="n">
-        <v>0.3244</v>
+        <v>0.2824</v>
       </c>
       <c r="J98" t="n">
-        <v>9.731999999999999</v>
+        <v>8.472</v>
       </c>
     </row>
     <row r="99">
@@ -5389,10 +5389,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2242</v>
+        <v>-0.1894</v>
       </c>
       <c r="J99" t="n">
-        <v>-6.726</v>
+        <v>-5.682</v>
       </c>
     </row>
     <row r="100">
@@ -5429,10 +5429,10 @@
         <v>0.93</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.253</v>
+        <v>-0.2161</v>
       </c>
       <c r="J100" t="n">
-        <v>-7.59</v>
+        <v>-6.483</v>
       </c>
     </row>
     <row r="101">
@@ -5469,10 +5469,10 @@
         <v>0.49</v>
       </c>
       <c r="I101" t="n">
-        <v>-1.2304</v>
+        <v>-1.2586</v>
       </c>
       <c r="J101" t="n">
-        <v>-36.912</v>
+        <v>-37.758</v>
       </c>
     </row>
     <row r="102">
@@ -5509,10 +5509,10 @@
         <v>0.98</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.0245</v>
+        <v>-0.0172</v>
       </c>
       <c r="J102" t="n">
-        <v>-0.637</v>
+        <v>-0.4472</v>
       </c>
     </row>
     <row r="103">
@@ -5549,10 +5549,10 @@
         <v>0.93</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.096</v>
+        <v>-0.0823</v>
       </c>
       <c r="J103" t="n">
-        <v>-2.496</v>
+        <v>-2.1398</v>
       </c>
     </row>
     <row r="104">
@@ -5589,10 +5589,10 @@
         <v>0.85</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1869</v>
+        <v>-0.1697</v>
       </c>
       <c r="J104" t="n">
-        <v>-4.8594</v>
+        <v>-4.4122</v>
       </c>
     </row>
     <row r="105">
@@ -5629,10 +5629,10 @@
         <v>0.76</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2739</v>
+        <v>-0.2559</v>
       </c>
       <c r="J105" t="n">
-        <v>-7.1214</v>
+        <v>-6.6534</v>
       </c>
     </row>
     <row r="106">
@@ -5669,10 +5669,10 @@
         <v>0.59</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4292</v>
+        <v>-0.4204</v>
       </c>
       <c r="J106" t="n">
-        <v>-11.1592</v>
+        <v>-10.9304</v>
       </c>
     </row>
     <row r="107">
@@ -5709,10 +5709,10 @@
         <v>1.62</v>
       </c>
       <c r="I107" t="n">
-        <v>1.1257</v>
+        <v>1.1196</v>
       </c>
       <c r="J107" t="n">
-        <v>29.2682</v>
+        <v>29.1096</v>
       </c>
     </row>
     <row r="108">
@@ -5749,10 +5749,10 @@
         <v>1.33</v>
       </c>
       <c r="I108" t="n">
-        <v>0.7198</v>
+        <v>0.7049</v>
       </c>
       <c r="J108" t="n">
-        <v>18.7148</v>
+        <v>18.3274</v>
       </c>
     </row>
     <row r="109">
@@ -5789,10 +5789,10 @@
         <v>1.2</v>
       </c>
       <c r="I109" t="n">
-        <v>0.5194</v>
+        <v>0.5089</v>
       </c>
       <c r="J109" t="n">
-        <v>13.5044</v>
+        <v>13.2314</v>
       </c>
     </row>
     <row r="110">
@@ -5829,10 +5829,10 @@
         <v>0.98</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1302</v>
+        <v>-0.103</v>
       </c>
       <c r="J110" t="n">
-        <v>-3.3852</v>
+        <v>-2.678</v>
       </c>
     </row>
     <row r="111">
@@ -5869,10 +5869,10 @@
         <v>0.74</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.755</v>
+        <v>-0.7299</v>
       </c>
       <c r="J111" t="n">
-        <v>-19.63</v>
+        <v>-18.9774</v>
       </c>
     </row>
     <row r="112">
@@ -5909,10 +5909,10 @@
         <v>1.48</v>
       </c>
       <c r="I112" t="n">
-        <v>0.9627</v>
+        <v>0.9512</v>
       </c>
       <c r="J112" t="n">
-        <v>28.881</v>
+        <v>28.536</v>
       </c>
     </row>
     <row r="113">
@@ -5949,10 +5949,10 @@
         <v>1.23</v>
       </c>
       <c r="I113" t="n">
-        <v>0.584</v>
+        <v>0.5718</v>
       </c>
       <c r="J113" t="n">
-        <v>17.52</v>
+        <v>17.154</v>
       </c>
     </row>
     <row r="114">
@@ -5989,10 +5989,10 @@
         <v>1.05</v>
       </c>
       <c r="I114" t="n">
-        <v>0.191</v>
+        <v>0.1605</v>
       </c>
       <c r="J114" t="n">
-        <v>5.73</v>
+        <v>4.815</v>
       </c>
     </row>
     <row r="115">
@@ -6029,10 +6029,10 @@
         <v>0.8</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.6012999999999999</v>
+        <v>-0.5633</v>
       </c>
       <c r="J115" t="n">
-        <v>-18.039</v>
+        <v>-16.899</v>
       </c>
     </row>
     <row r="116">
@@ -6069,10 +6069,10 @@
         <v>0.78</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.647</v>
+        <v>-0.6115</v>
       </c>
       <c r="J116" t="n">
-        <v>-19.41</v>
+        <v>-18.345</v>
       </c>
     </row>
     <row r="117">
@@ -6109,10 +6109,10 @@
         <v>1.08</v>
       </c>
       <c r="I117" t="n">
-        <v>0.2292</v>
+        <v>0.1847</v>
       </c>
       <c r="J117" t="n">
-        <v>6.876</v>
+        <v>5.541</v>
       </c>
     </row>
     <row r="118">
@@ -6149,10 +6149,10 @@
         <v>1.05</v>
       </c>
       <c r="I118" t="n">
-        <v>0.163</v>
+        <v>0.1261</v>
       </c>
       <c r="J118" t="n">
-        <v>4.89</v>
+        <v>3.783</v>
       </c>
     </row>
     <row r="119">
@@ -6189,10 +6189,10 @@
         <v>0.93</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.1061</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="J119" t="n">
-        <v>-3.183</v>
+        <v>-2.709</v>
       </c>
     </row>
     <row r="120">
@@ -6229,10 +6229,10 @@
         <v>0.85</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1941</v>
+        <v>-0.1742</v>
       </c>
       <c r="J120" t="n">
-        <v>-5.823</v>
+        <v>-5.226</v>
       </c>
     </row>
     <row r="121">
@@ -6269,10 +6269,10 @@
         <v>0.68</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3584</v>
+        <v>-0.3438</v>
       </c>
       <c r="J121" t="n">
-        <v>-10.752</v>
+        <v>-10.314</v>
       </c>
     </row>
     <row r="122">
@@ -6309,10 +6309,10 @@
         <v>1.46</v>
       </c>
       <c r="I122" t="n">
-        <v>0.9016</v>
+        <v>0.8866000000000001</v>
       </c>
       <c r="J122" t="n">
-        <v>22.54</v>
+        <v>22.165</v>
       </c>
     </row>
     <row r="123">
@@ -6349,10 +6349,10 @@
         <v>1.44</v>
       </c>
       <c r="I123" t="n">
-        <v>0.8736</v>
+        <v>0.8582</v>
       </c>
       <c r="J123" t="n">
-        <v>21.84</v>
+        <v>21.455</v>
       </c>
     </row>
     <row r="124">
@@ -6389,10 +6389,10 @@
         <v>1.11</v>
       </c>
       <c r="I124" t="n">
-        <v>0.336</v>
+        <v>0.3026</v>
       </c>
       <c r="J124" t="n">
-        <v>8.4</v>
+        <v>7.565</v>
       </c>
     </row>
     <row r="125">
@@ -6429,10 +6429,10 @@
         <v>1.04</v>
       </c>
       <c r="I125" t="n">
-        <v>0.1378</v>
+        <v>0.1141</v>
       </c>
       <c r="J125" t="n">
-        <v>3.445</v>
+        <v>2.8525</v>
       </c>
     </row>
     <row r="126">
@@ -6469,10 +6469,10 @@
         <v>0.95</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.2373</v>
+        <v>-0.2007</v>
       </c>
       <c r="J126" t="n">
-        <v>-5.9325</v>
+        <v>-5.0175</v>
       </c>
     </row>
     <row r="127">
@@ -6509,10 +6509,10 @@
         <v>0.98</v>
       </c>
       <c r="I127" t="n">
-        <v>-0.0149</v>
+        <v>-0.0068</v>
       </c>
       <c r="J127" t="n">
-        <v>-0.3725</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="128">
@@ -6549,10 +6549,10 @@
         <v>0.77</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.2602</v>
+        <v>-0.2436</v>
       </c>
       <c r="J128" t="n">
-        <v>-6.505</v>
+        <v>-6.09</v>
       </c>
     </row>
     <row r="129">
@@ -6589,10 +6589,10 @@
         <v>0.74</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2875</v>
+        <v>-0.271</v>
       </c>
       <c r="J129" t="n">
-        <v>-7.1875</v>
+        <v>-6.775</v>
       </c>
     </row>
     <row r="130">
@@ -6629,10 +6629,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3334</v>
+        <v>-0.318</v>
       </c>
       <c r="J130" t="n">
-        <v>-8.335000000000001</v>
+        <v>-7.95</v>
       </c>
     </row>
     <row r="131">
@@ -6669,10 +6669,10 @@
         <v>0.67</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3516</v>
+        <v>-0.337</v>
       </c>
       <c r="J131" t="n">
-        <v>-8.789999999999999</v>
+        <v>-8.425000000000001</v>
       </c>
     </row>
   </sheetData>
